--- a/site/exports/thu-ee-communications.xlsx
+++ b/site/exports/thu-ee-communications.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R415a2c3052004aec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R89fb6941d26f4ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rb06fb88797864d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R303609f49a564a54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R287756bc00594aec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R57238adf11584adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R461c4c3f8af94f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R64924e7bdb7c4d77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R4e563b732f0046df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rdf638849327c4c2f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T9_0" displayName="T9_0" ref="A1:K6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T9_0" displayName="T9_0" ref="A1:K11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T9_1" displayName="T9_1" ref="A1:S42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T9_1" displayName="T9_1" ref="A1:S86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T9_3" displayName="T9_3" ref="A1:L14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T9_3" displayName="T9_3" ref="A1:L23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T9_4" displayName="T9_4" ref="A1:G43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T9_4" displayName="T9_4" ref="A1:G68" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -647,10 +647,175 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>未核各阶段直接导师；教材合著与学术合作不推师承。；没有单独硕士学位条目，不从博士学位推硕士；教育专业字段仅院系，精确专业未披露。；访问均为非授位岗位；中文密歇根校名冲突已保留。</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>本人导师、博士后合作导师未核；不从同实验室曾烈光/金德鹏或论文合著推定。；硕士单列仅英文，博士总区间包含此前学习，不编造分段。；海外短访与博士后不是第二个授位学历。</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/lujianhua/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>集中主页教育工作为空，由校级院士简介补三学位。；香港学位country中国、region中国香港，与内地授位分层，不自动归国外或内地。；导师与精选逐篇论文未核；只列200余篇总量不当个人书目。；校级简介列基金委职务，未进一步核当期领导，不添加其现任外部职务。</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>硕博起止年份和直接导师未核，转载1997/1999不进入确证字段。；历史西南师范大学保留原名，不误并985西南交通大学；现合并西南大学不代表当年授位主体变更。；主页未列教授/研究员职称，当前只留教授栏目与无线中心副主任；校友页2017称研究员，不冒称当期职称。；个人精选论文尚未取得出版者原始元数据，保持空。</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>各阶段导师未核；日企研究员与各国短访不是额外学位。；本科保留北方交通大学历史校名，不能按名称相似误归西安/上海交通大学。；部分短访重叠照录，不推全职排他任职。</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61bdf7d872fd4a5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racbb202377704da8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2562,10 +2727,1904 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="43" ht="64" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>西安交通大学</x:v>
+      </x:c>
+      <x:c r="E43" s="6" t="str">
+        <x:v>1994-09</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>1998-07</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>信息与通信工程系（院系原文）</x:v>
+      </x:c>
+      <x:c r="H43" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I43" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J43" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K43" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L43" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M43" s="7" t="str"/>
+      <x:c r="N43" s="6" t="str"/>
+      <x:c r="O43" s="6" t="str"/>
+      <x:c r="P43" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q43" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R43" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S43" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E44" s="6" t="str">
+        <x:v>1998-09</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>电子工程系（院系原文）</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I44" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J44" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K44" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L44" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M44" s="7" t="str"/>
+      <x:c r="N44" s="6" t="str"/>
+      <x:c r="O44" s="6" t="str"/>
+      <x:c r="P44" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q44" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R44" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S44" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E45" s="6" t="str">
+        <x:v>2003-08</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>2006-12</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str"/>
+      <x:c r="H45" s="6" t="str"/>
+      <x:c r="I45" s="6" t="str"/>
+      <x:c r="J45" s="6" t="str"/>
+      <x:c r="K45" s="6" t="str"/>
+      <x:c r="L45" s="6" t="str"/>
+      <x:c r="M45" s="7" t="str"/>
+      <x:c r="N45" s="6" t="str"/>
+      <x:c r="O45" s="6" t="str"/>
+      <x:c r="P45" s="6" t="str"/>
+      <x:c r="Q45" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R45" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S45" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>副教授/准聘副教授/长聘副教授</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E46" s="6" t="str">
+        <x:v>2006-12</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="str">
+        <x:v>2018-12</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="str"/>
+      <x:c r="H46" s="6" t="str"/>
+      <x:c r="I46" s="6" t="str"/>
+      <x:c r="J46" s="6" t="str"/>
+      <x:c r="K46" s="6" t="str"/>
+      <x:c r="L46" s="6" t="str"/>
+      <x:c r="M46" s="7" t="str"/>
+      <x:c r="N46" s="6" t="str"/>
+      <x:c r="O46" s="6" t="str"/>
+      <x:c r="P46" s="6" t="str"/>
+      <x:c r="Q46" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R46" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S46" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E47" s="6" t="str">
+        <x:v>2018-12</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str"/>
+      <x:c r="G47" s="6" t="str"/>
+      <x:c r="H47" s="6" t="str"/>
+      <x:c r="I47" s="6" t="str"/>
+      <x:c r="J47" s="6" t="str"/>
+      <x:c r="K47" s="6" t="str"/>
+      <x:c r="L47" s="6" t="str"/>
+      <x:c r="M47" s="7" t="str"/>
+      <x:c r="N47" s="6" t="str"/>
+      <x:c r="O47" s="6" t="str"/>
+      <x:c r="P47" s="6" t="str"/>
+      <x:c r="Q47" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R47" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S47" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>麻省理工学院电气工程与计算机科学系</x:v>
+      </x:c>
+      <x:c r="E48" s="6" t="str">
+        <x:v>2012-08</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="str">
+        <x:v>2013-05</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str"/>
+      <x:c r="H48" s="6" t="str"/>
+      <x:c r="I48" s="6" t="str"/>
+      <x:c r="J48" s="6" t="str"/>
+      <x:c r="K48" s="6" t="str"/>
+      <x:c r="L48" s="6" t="str"/>
+      <x:c r="M48" s="7" t="str"/>
+      <x:c r="N48" s="6" t="str"/>
+      <x:c r="O48" s="6" t="str"/>
+      <x:c r="P48" s="6" t="str"/>
+      <x:c r="Q48" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R48" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S48" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>斯坦福大学电气工程与计算机科学系</x:v>
+      </x:c>
+      <x:c r="E49" s="6" t="str">
+        <x:v>2013-05</x:v>
+      </x:c>
+      <x:c r="F49" s="6" t="str">
+        <x:v>2013-08</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str"/>
+      <x:c r="H49" s="6" t="str"/>
+      <x:c r="I49" s="6" t="str"/>
+      <x:c r="J49" s="6" t="str"/>
+      <x:c r="K49" s="6" t="str"/>
+      <x:c r="L49" s="6" t="str"/>
+      <x:c r="M49" s="7" t="str"/>
+      <x:c r="N49" s="6" t="str"/>
+      <x:c r="O49" s="6" t="str"/>
+      <x:c r="P49" s="6" t="str"/>
+      <x:c r="Q49" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R49" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S49" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>高级访问学者/访问教授</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>密歇根大学安娜堡分校</x:v>
+      </x:c>
+      <x:c r="E50" s="6" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="str">
+        <x:v>2015-10</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str"/>
+      <x:c r="H50" s="6" t="str"/>
+      <x:c r="I50" s="6" t="str"/>
+      <x:c r="J50" s="6" t="str"/>
+      <x:c r="K50" s="6" t="str"/>
+      <x:c r="L50" s="6" t="str"/>
+      <x:c r="M50" s="7" t="str"/>
+      <x:c r="N50" s="6" t="str"/>
+      <x:c r="O50" s="6" t="str">
+        <x:v>中文误合“密歇根州立大学安娜堡分校”；英文明确University of Michigan at Ann Arbor，成电官方讲座简介也为密歇根大学，按英文规范机构且保留冲突。</x:v>
+      </x:c>
+      <x:c r="P50" s="6" t="str"/>
+      <x:c r="Q50" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/en/index.htm</x:v>
+      </x:c>
+      <x:c r="R50" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S50" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>微软亚洲研究院</x:v>
+      </x:c>
+      <x:c r="E51" s="6" t="str">
+        <x:v>2005-12</x:v>
+      </x:c>
+      <x:c r="F51" s="6" t="str">
+        <x:v>2006-02</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str"/>
+      <x:c r="H51" s="6" t="str"/>
+      <x:c r="I51" s="6" t="str"/>
+      <x:c r="J51" s="6" t="str"/>
+      <x:c r="K51" s="6" t="str"/>
+      <x:c r="L51" s="6" t="str"/>
+      <x:c r="M51" s="7" t="str"/>
+      <x:c r="N51" s="6" t="str"/>
+      <x:c r="O51" s="6" t="str"/>
+      <x:c r="P51" s="6" t="str"/>
+      <x:c r="Q51" s="6" t="str">
+        <x:v>https://news.uestc.edu.cn/info/1009/15036.htm</x:v>
+      </x:c>
+      <x:c r="R51" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S51" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>华中科技大学</x:v>
+      </x:c>
+      <x:c r="E52" s="6" t="str">
+        <x:v>2003-09</x:v>
+      </x:c>
+      <x:c r="F52" s="6" t="str">
+        <x:v>2007-07</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="str">
+        <x:v>电子与信息工程系（院系原文）</x:v>
+      </x:c>
+      <x:c r="H52" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I52" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J52" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K52" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L52" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M52" s="7" t="str"/>
+      <x:c r="N52" s="6" t="str"/>
+      <x:c r="O52" s="6" t="str"/>
+      <x:c r="P52" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q52" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R52" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S52" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E53" s="6" t="str"/>
+      <x:c r="F53" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="str">
+        <x:v>Electrical Engineering</x:v>
+      </x:c>
+      <x:c r="H53" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I53" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J53" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K53" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L53" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M53" s="7" t="str"/>
+      <x:c r="N53" s="6" t="str"/>
+      <x:c r="O53" s="6" t="str">
+        <x:v>自管官方英文主页明确2009获硕士，集中中文主页未单列；不猜硕士入学月。</x:v>
+      </x:c>
+      <x:c r="P53" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q53" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/~liyong/</x:v>
+      </x:c>
+      <x:c r="R53" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S53" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E54" s="6" t="str">
+        <x:v>2007-09</x:v>
+      </x:c>
+      <x:c r="F54" s="6" t="str">
+        <x:v>2012-06</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H54" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I54" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J54" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K54" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L54" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M54" s="7" t="str"/>
+      <x:c r="N54" s="6" t="str"/>
+      <x:c r="O54" s="6" t="str">
+        <x:v>集中主页博士总学习区间2007.09–2012.06；英文另明确2009硕士，两字段并存，不改成博士始于2009。</x:v>
+      </x:c>
+      <x:c r="P54" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q54" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R54" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S54" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E55" s="6" t="str">
+        <x:v>2012-06</x:v>
+      </x:c>
+      <x:c r="F55" s="6" t="str">
+        <x:v>2014-05</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="str"/>
+      <x:c r="H55" s="6" t="str"/>
+      <x:c r="I55" s="6" t="str"/>
+      <x:c r="J55" s="6" t="str"/>
+      <x:c r="K55" s="6" t="str"/>
+      <x:c r="L55" s="6" t="str"/>
+      <x:c r="M55" s="7" t="str"/>
+      <x:c r="N55" s="6" t="str"/>
+      <x:c r="O55" s="6" t="str"/>
+      <x:c r="P55" s="6" t="str"/>
+      <x:c r="Q55" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R55" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S55" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="str">
+        <x:v>助理教授、副教授、教授</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E56" s="6" t="str">
+        <x:v>2014-06</x:v>
+      </x:c>
+      <x:c r="F56" s="6" t="str"/>
+      <x:c r="G56" s="6" t="str"/>
+      <x:c r="H56" s="6" t="str"/>
+      <x:c r="I56" s="6" t="str"/>
+      <x:c r="J56" s="6" t="str"/>
+      <x:c r="K56" s="6" t="str"/>
+      <x:c r="L56" s="6" t="str"/>
+      <x:c r="M56" s="7" t="str"/>
+      <x:c r="N56" s="6" t="str"/>
+      <x:c r="O56" s="6" t="str">
+        <x:v>原表合并任职，不拆造各晋升年份。现正文长聘教授。</x:v>
+      </x:c>
+      <x:c r="P56" s="6" t="str"/>
+      <x:c r="Q56" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R56" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S56" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
+        <x:v>美国迈阿密大学物理系/电子与计算机工程系</x:v>
+      </x:c>
+      <x:c r="E57" s="6" t="str">
+        <x:v>2013-12</x:v>
+      </x:c>
+      <x:c r="F57" s="6" t="str">
+        <x:v>2014-03</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str"/>
+      <x:c r="H57" s="6" t="str"/>
+      <x:c r="I57" s="6" t="str"/>
+      <x:c r="J57" s="6" t="str"/>
+      <x:c r="K57" s="6" t="str"/>
+      <x:c r="L57" s="6" t="str"/>
+      <x:c r="M57" s="7" t="str"/>
+      <x:c r="N57" s="6" t="str"/>
+      <x:c r="O57" s="6" t="str"/>
+      <x:c r="P57" s="6" t="str"/>
+      <x:c r="Q57" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R57" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S57" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="str">
+        <x:v>访问研究助理</x:v>
+      </x:c>
+      <x:c r="D58" s="6" t="str">
+        <x:v>Telekom Innovation Laboratories</x:v>
+      </x:c>
+      <x:c r="E58" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str"/>
+      <x:c r="H58" s="6" t="str"/>
+      <x:c r="I58" s="6" t="str"/>
+      <x:c r="J58" s="6" t="str"/>
+      <x:c r="K58" s="6" t="str"/>
+      <x:c r="L58" s="6" t="str"/>
+      <x:c r="M58" s="7" t="str"/>
+      <x:c r="N58" s="6" t="str"/>
+      <x:c r="O58" s="6" t="str">
+        <x:v>英文只给发生年份，非完整起止日；地点未单独核。</x:v>
+      </x:c>
+      <x:c r="P58" s="6" t="str"/>
+      <x:c r="Q58" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/~liyong/</x:v>
+      </x:c>
+      <x:c r="R58" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S58" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>访问研究助理</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
+        <x:v>香港科技大学</x:v>
+      </x:c>
+      <x:c r="E59" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="F59" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="str"/>
+      <x:c r="H59" s="6" t="str"/>
+      <x:c r="I59" s="6" t="str"/>
+      <x:c r="J59" s="6" t="str"/>
+      <x:c r="K59" s="6" t="str"/>
+      <x:c r="L59" s="6" t="str"/>
+      <x:c r="M59" s="7" t="str"/>
+      <x:c r="N59" s="6" t="str"/>
+      <x:c r="O59" s="6" t="str">
+        <x:v>年份级经历，非授位。</x:v>
+      </x:c>
+      <x:c r="P59" s="6" t="str"/>
+      <x:c r="Q59" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/~liyong/</x:v>
+      </x:c>
+      <x:c r="R59" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S59" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D60" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E60" s="6" t="str"/>
+      <x:c r="F60" s="6" t="str">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="str"/>
+      <x:c r="H60" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I60" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J60" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K60" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L60" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M60" s="7" t="str"/>
+      <x:c r="N60" s="6" t="str"/>
+      <x:c r="O60" s="6" t="str">
+        <x:v>清华院士页明确获学位；起始日期与博士具体专业未披露。</x:v>
+      </x:c>
+      <x:c r="P60" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q60" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="R60" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S60" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C61" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D61" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E61" s="6" t="str"/>
+      <x:c r="F61" s="6" t="str">
+        <x:v>1989</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str"/>
+      <x:c r="H61" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I61" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J61" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K61" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L61" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M61" s="7" t="str"/>
+      <x:c r="N61" s="6" t="str"/>
+      <x:c r="O61" s="6" t="str">
+        <x:v>清华院士页明确获学位；起始日期与博士具体专业未披露。</x:v>
+      </x:c>
+      <x:c r="P61" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q61" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="R61" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S61" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C62" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
+        <x:v>香港科技大学</x:v>
+      </x:c>
+      <x:c r="E62" s="6" t="str"/>
+      <x:c r="F62" s="6" t="str">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="G62" s="6" t="str"/>
+      <x:c r="H62" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I62" s="6" t="str">
+        <x:v>中国香港</x:v>
+      </x:c>
+      <x:c r="J62" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K62" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L62" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M62" s="7" t="str"/>
+      <x:c r="N62" s="6" t="str"/>
+      <x:c r="O62" s="6" t="str">
+        <x:v>清华院士页明确获学位；起始日期与博士具体专业未披露。</x:v>
+      </x:c>
+      <x:c r="P62" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q62" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="R62" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S62" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D63" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E63" s="6" t="str"/>
+      <x:c r="F63" s="6" t="str"/>
+      <x:c r="G63" s="6" t="str"/>
+      <x:c r="H63" s="6" t="str"/>
+      <x:c r="I63" s="6" t="str"/>
+      <x:c r="J63" s="6" t="str"/>
+      <x:c r="K63" s="6" t="str"/>
+      <x:c r="L63" s="6" t="str"/>
+      <x:c r="M63" s="7" t="str"/>
+      <x:c r="N63" s="6" t="str"/>
+      <x:c r="O63" s="6" t="str"/>
+      <x:c r="P63" s="6" t="str"/>
+      <x:c r="Q63" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/lujianhua/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R63" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S63" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C64" s="6" t="str">
+        <x:v>留校任教</x:v>
+      </x:c>
+      <x:c r="D64" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E64" s="6" t="str">
+        <x:v>1989</x:v>
+      </x:c>
+      <x:c r="F64" s="6" t="str"/>
+      <x:c r="G64" s="6" t="str"/>
+      <x:c r="H64" s="6" t="str"/>
+      <x:c r="I64" s="6" t="str"/>
+      <x:c r="J64" s="6" t="str"/>
+      <x:c r="K64" s="6" t="str"/>
+      <x:c r="L64" s="6" t="str"/>
+      <x:c r="M64" s="7" t="str"/>
+      <x:c r="N64" s="6" t="str"/>
+      <x:c r="O64" s="6" t="str">
+        <x:v>原文入职1989，不把该年当教授晋升年。</x:v>
+      </x:c>
+      <x:c r="P64" s="6" t="str"/>
+      <x:c r="Q64" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="R64" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S64" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
+      <x:c r="A65" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C65" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D65" s="6" t="str">
+        <x:v>西南师范大学</x:v>
+      </x:c>
+      <x:c r="E65" s="6" t="str"/>
+      <x:c r="F65" s="6" t="str">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="G65" s="6" t="str">
+        <x:v>物理学</x:v>
+      </x:c>
+      <x:c r="H65" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I65" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J65" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K65" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L65" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M65" s="7" t="str"/>
+      <x:c r="N65" s="6" t="str"/>
+      <x:c r="O65" s="6" t="str">
+        <x:v>本科毕业年份/学科由西南大学官方校友页确认，学士学位由本人清华主页明确。</x:v>
+      </x:c>
+      <x:c r="P65" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q65" s="6" t="str">
+        <x:v>https://physics.swu.edu.cn/info/1077/2131.htm</x:v>
+      </x:c>
+      <x:c r="R65" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S65" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C66" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D66" s="6" t="str">
+        <x:v>电子科技大学</x:v>
+      </x:c>
+      <x:c r="E66" s="6" t="str"/>
+      <x:c r="F66" s="6" t="str"/>
+      <x:c r="G66" s="6" t="str"/>
+      <x:c r="H66" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I66" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J66" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K66" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L66" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M66" s="7" t="str"/>
+      <x:c r="N66" s="6" t="str"/>
+      <x:c r="O66" s="6" t="str">
+        <x:v>本人明确工学硕士，无年份，不采用转载1997。</x:v>
+      </x:c>
+      <x:c r="P66" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q66" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R66" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S66" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="64" customHeight="1">
+      <x:c r="A67" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C67" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D67" s="6" t="str">
+        <x:v>电子科技大学</x:v>
+      </x:c>
+      <x:c r="E67" s="6" t="str"/>
+      <x:c r="F67" s="6" t="str"/>
+      <x:c r="G67" s="6" t="str"/>
+      <x:c r="H67" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I67" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J67" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K67" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L67" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M67" s="7" t="str"/>
+      <x:c r="N67" s="6" t="str"/>
+      <x:c r="O67" s="6" t="str">
+        <x:v>本人明确工学博士，无年份，不采用转载1999。</x:v>
+      </x:c>
+      <x:c r="P67" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q67" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R67" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S67" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="64" customHeight="1">
+      <x:c r="A68" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C68" s="6" t="str">
+        <x:v>教师</x:v>
+      </x:c>
+      <x:c r="D68" s="6" t="str">
+        <x:v>西南师范大学</x:v>
+      </x:c>
+      <x:c r="E68" s="6" t="str">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="F68" s="6" t="str">
+        <x:v>1994</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str"/>
+      <x:c r="H68" s="6" t="str"/>
+      <x:c r="I68" s="6" t="str"/>
+      <x:c r="J68" s="6" t="str"/>
+      <x:c r="K68" s="6" t="str"/>
+      <x:c r="L68" s="6" t="str"/>
+      <x:c r="M68" s="7" t="str"/>
+      <x:c r="N68" s="6" t="str"/>
+      <x:c r="O68" s="6" t="str"/>
+      <x:c r="P68" s="6" t="str"/>
+      <x:c r="Q68" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R68" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S68" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64" customHeight="1">
+      <x:c r="A69" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C69" s="6" t="str">
+        <x:v>任职</x:v>
+      </x:c>
+      <x:c r="D69" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E69" s="6" t="str">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="F69" s="6" t="str"/>
+      <x:c r="G69" s="6" t="str"/>
+      <x:c r="H69" s="6" t="str"/>
+      <x:c r="I69" s="6" t="str"/>
+      <x:c r="J69" s="6" t="str"/>
+      <x:c r="K69" s="6" t="str"/>
+      <x:c r="L69" s="6" t="str"/>
+      <x:c r="M69" s="7" t="str"/>
+      <x:c r="N69" s="6" t="str"/>
+      <x:c r="O69" s="6" t="str">
+        <x:v>本人工作经历列1999至今，具体职称晋升日期未列。</x:v>
+      </x:c>
+      <x:c r="P69" s="6" t="str"/>
+      <x:c r="Q69" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R69" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S69" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="64" customHeight="1">
+      <x:c r="A70" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B70" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C70" s="6" t="str">
+        <x:v>副主任</x:v>
+      </x:c>
+      <x:c r="D70" s="6" t="str">
+        <x:v>清华大学无线中心</x:v>
+      </x:c>
+      <x:c r="E70" s="6" t="str"/>
+      <x:c r="F70" s="6" t="str"/>
+      <x:c r="G70" s="6" t="str"/>
+      <x:c r="H70" s="6" t="str"/>
+      <x:c r="I70" s="6" t="str"/>
+      <x:c r="J70" s="6" t="str"/>
+      <x:c r="K70" s="6" t="str"/>
+      <x:c r="L70" s="6" t="str"/>
+      <x:c r="M70" s="7" t="str"/>
+      <x:c r="N70" s="6" t="str"/>
+      <x:c r="O70" s="6" t="str"/>
+      <x:c r="P70" s="6" t="str"/>
+      <x:c r="Q70" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R70" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S70" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
+      <x:c r="A71" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C71" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D71" s="6" t="str">
+        <x:v>北方交通大学</x:v>
+      </x:c>
+      <x:c r="E71" s="6" t="str">
+        <x:v>1981-09</x:v>
+      </x:c>
+      <x:c r="F71" s="6" t="str">
+        <x:v>1985-07</x:v>
+      </x:c>
+      <x:c r="G71" s="6" t="str">
+        <x:v>通信与控制系（院系原文）</x:v>
+      </x:c>
+      <x:c r="H71" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I71" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J71" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K71" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L71" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M71" s="7" t="str"/>
+      <x:c r="N71" s="6" t="str"/>
+      <x:c r="O71" s="6" t="str"/>
+      <x:c r="P71" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q71" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R71" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S71" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="64" customHeight="1">
+      <x:c r="A72" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B72" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C72" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D72" s="6" t="str">
+        <x:v>丰桥技术科学大学</x:v>
+      </x:c>
+      <x:c r="E72" s="6" t="str">
+        <x:v>1986-10</x:v>
+      </x:c>
+      <x:c r="F72" s="6" t="str">
+        <x:v>1989-03</x:v>
+      </x:c>
+      <x:c r="G72" s="6" t="str">
+        <x:v>信息工学</x:v>
+      </x:c>
+      <x:c r="H72" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="I72" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="J72" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K72" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L72" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M72" s="7" t="str"/>
+      <x:c r="N72" s="6" t="str"/>
+      <x:c r="O72" s="6" t="str"/>
+      <x:c r="P72" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q72" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R72" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S72" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="64" customHeight="1">
+      <x:c r="A73" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B73" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C73" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D73" s="6" t="str">
+        <x:v>丰桥技术科学大学</x:v>
+      </x:c>
+      <x:c r="E73" s="6" t="str">
+        <x:v>1989-04</x:v>
+      </x:c>
+      <x:c r="F73" s="6" t="str">
+        <x:v>1992-03</x:v>
+      </x:c>
+      <x:c r="G73" s="6" t="str">
+        <x:v>系统工学</x:v>
+      </x:c>
+      <x:c r="H73" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="I73" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="J73" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K73" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L73" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M73" s="7" t="str"/>
+      <x:c r="N73" s="6" t="str"/>
+      <x:c r="O73" s="6" t="str"/>
+      <x:c r="P73" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q73" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R73" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S73" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="64" customHeight="1">
+      <x:c r="A74" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B74" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C74" s="6" t="str">
+        <x:v>特别研究员</x:v>
+      </x:c>
+      <x:c r="D74" s="6" t="str">
+        <x:v>富士通研究所综合通信研究部</x:v>
+      </x:c>
+      <x:c r="E74" s="6" t="str">
+        <x:v>1992-04</x:v>
+      </x:c>
+      <x:c r="F74" s="6" t="str">
+        <x:v>1994-03</x:v>
+      </x:c>
+      <x:c r="G74" s="6" t="str"/>
+      <x:c r="H74" s="6" t="str"/>
+      <x:c r="I74" s="6" t="str"/>
+      <x:c r="J74" s="6" t="str"/>
+      <x:c r="K74" s="6" t="str"/>
+      <x:c r="L74" s="6" t="str"/>
+      <x:c r="M74" s="7" t="str"/>
+      <x:c r="N74" s="6" t="str"/>
+      <x:c r="O74" s="6" t="str"/>
+      <x:c r="P74" s="6" t="str"/>
+      <x:c r="Q74" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R74" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S74" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="64" customHeight="1">
+      <x:c r="A75" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B75" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C75" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D75" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E75" s="6" t="str">
+        <x:v>1994-04</x:v>
+      </x:c>
+      <x:c r="F75" s="6" t="str">
+        <x:v>1994-11</x:v>
+      </x:c>
+      <x:c r="G75" s="6" t="str"/>
+      <x:c r="H75" s="6" t="str"/>
+      <x:c r="I75" s="6" t="str"/>
+      <x:c r="J75" s="6" t="str"/>
+      <x:c r="K75" s="6" t="str"/>
+      <x:c r="L75" s="6" t="str"/>
+      <x:c r="M75" s="7" t="str"/>
+      <x:c r="N75" s="6" t="str"/>
+      <x:c r="O75" s="6" t="str"/>
+      <x:c r="P75" s="6" t="str"/>
+      <x:c r="Q75" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R75" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S75" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="64" customHeight="1">
+      <x:c r="A76" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B76" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C76" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D76" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E76" s="6" t="str">
+        <x:v>1994-12</x:v>
+      </x:c>
+      <x:c r="F76" s="6" t="str">
+        <x:v>1999-11</x:v>
+      </x:c>
+      <x:c r="G76" s="6" t="str"/>
+      <x:c r="H76" s="6" t="str"/>
+      <x:c r="I76" s="6" t="str"/>
+      <x:c r="J76" s="6" t="str"/>
+      <x:c r="K76" s="6" t="str"/>
+      <x:c r="L76" s="6" t="str"/>
+      <x:c r="M76" s="7" t="str"/>
+      <x:c r="N76" s="6" t="str"/>
+      <x:c r="O76" s="6" t="str"/>
+      <x:c r="P76" s="6" t="str"/>
+      <x:c r="Q76" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R76" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S76" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64" customHeight="1">
+      <x:c r="A77" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B77" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C77" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D77" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E77" s="6" t="str">
+        <x:v>1999-12</x:v>
+      </x:c>
+      <x:c r="F77" s="6" t="str"/>
+      <x:c r="G77" s="6" t="str"/>
+      <x:c r="H77" s="6" t="str"/>
+      <x:c r="I77" s="6" t="str"/>
+      <x:c r="J77" s="6" t="str"/>
+      <x:c r="K77" s="6" t="str"/>
+      <x:c r="L77" s="6" t="str"/>
+      <x:c r="M77" s="7" t="str"/>
+      <x:c r="N77" s="6" t="str"/>
+      <x:c r="O77" s="6" t="str"/>
+      <x:c r="P77" s="6" t="str"/>
+      <x:c r="Q77" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R77" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S77" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="64" customHeight="1">
+      <x:c r="A78" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B78" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C78" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D78" s="6" t="str">
+        <x:v>南加州大学</x:v>
+      </x:c>
+      <x:c r="E78" s="6" t="str">
+        <x:v>2014-11</x:v>
+      </x:c>
+      <x:c r="F78" s="6" t="str">
+        <x:v>2014-12</x:v>
+      </x:c>
+      <x:c r="G78" s="6" t="str"/>
+      <x:c r="H78" s="6" t="str"/>
+      <x:c r="I78" s="6" t="str"/>
+      <x:c r="J78" s="6" t="str"/>
+      <x:c r="K78" s="6" t="str"/>
+      <x:c r="L78" s="6" t="str"/>
+      <x:c r="M78" s="7" t="str"/>
+      <x:c r="N78" s="6" t="str"/>
+      <x:c r="O78" s="6" t="str"/>
+      <x:c r="P78" s="6" t="str"/>
+      <x:c r="Q78" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R78" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S78" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="64" customHeight="1">
+      <x:c r="A79" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B79" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C79" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D79" s="6" t="str">
+        <x:v>汉堡大学</x:v>
+      </x:c>
+      <x:c r="E79" s="6" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="F79" s="6" t="str">
+        <x:v>2014-10</x:v>
+      </x:c>
+      <x:c r="G79" s="6" t="str"/>
+      <x:c r="H79" s="6" t="str"/>
+      <x:c r="I79" s="6" t="str"/>
+      <x:c r="J79" s="6" t="str"/>
+      <x:c r="K79" s="6" t="str"/>
+      <x:c r="L79" s="6" t="str"/>
+      <x:c r="M79" s="7" t="str"/>
+      <x:c r="N79" s="6" t="str"/>
+      <x:c r="O79" s="6" t="str"/>
+      <x:c r="P79" s="6" t="str"/>
+      <x:c r="Q79" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R79" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S79" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="64" customHeight="1">
+      <x:c r="A80" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B80" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C80" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D80" s="6" t="str">
+        <x:v>Polytechnic University, New York</x:v>
+      </x:c>
+      <x:c r="E80" s="6" t="str">
+        <x:v>2002-01</x:v>
+      </x:c>
+      <x:c r="F80" s="6" t="str">
+        <x:v>2002-02</x:v>
+      </x:c>
+      <x:c r="G80" s="6" t="str"/>
+      <x:c r="H80" s="6" t="str"/>
+      <x:c r="I80" s="6" t="str"/>
+      <x:c r="J80" s="6" t="str"/>
+      <x:c r="K80" s="6" t="str"/>
+      <x:c r="L80" s="6" t="str"/>
+      <x:c r="M80" s="7" t="str"/>
+      <x:c r="N80" s="6" t="str"/>
+      <x:c r="O80" s="6" t="str"/>
+      <x:c r="P80" s="6" t="str"/>
+      <x:c r="Q80" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R80" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S80" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="64" customHeight="1">
+      <x:c r="A81" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B81" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C81" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D81" s="6" t="str">
+        <x:v>佐贺大学</x:v>
+      </x:c>
+      <x:c r="E81" s="6" t="str">
+        <x:v>2001-01</x:v>
+      </x:c>
+      <x:c r="F81" s="6" t="str">
+        <x:v>2001-02</x:v>
+      </x:c>
+      <x:c r="G81" s="6" t="str"/>
+      <x:c r="H81" s="6" t="str"/>
+      <x:c r="I81" s="6" t="str"/>
+      <x:c r="J81" s="6" t="str"/>
+      <x:c r="K81" s="6" t="str"/>
+      <x:c r="L81" s="6" t="str"/>
+      <x:c r="M81" s="7" t="str"/>
+      <x:c r="N81" s="6" t="str"/>
+      <x:c r="O81" s="6" t="str"/>
+      <x:c r="P81" s="6" t="str"/>
+      <x:c r="Q81" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R81" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S81" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="64" customHeight="1">
+      <x:c r="A82" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B82" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C82" s="6" t="str">
+        <x:v>HIVIPS计划高级访问学者</x:v>
+      </x:c>
+      <x:c r="D82" s="6" t="str">
+        <x:v>日立公司中央研究所</x:v>
+      </x:c>
+      <x:c r="E82" s="6" t="str">
+        <x:v>1997-02</x:v>
+      </x:c>
+      <x:c r="F82" s="6" t="str">
+        <x:v>1998-02</x:v>
+      </x:c>
+      <x:c r="G82" s="6" t="str"/>
+      <x:c r="H82" s="6" t="str"/>
+      <x:c r="I82" s="6" t="str"/>
+      <x:c r="J82" s="6" t="str"/>
+      <x:c r="K82" s="6" t="str"/>
+      <x:c r="L82" s="6" t="str"/>
+      <x:c r="M82" s="7" t="str"/>
+      <x:c r="N82" s="6" t="str"/>
+      <x:c r="O82" s="6" t="str"/>
+      <x:c r="P82" s="6" t="str"/>
+      <x:c r="Q82" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R82" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S82" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="64" customHeight="1">
+      <x:c r="A83" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B83" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C83" s="6" t="str">
+        <x:v>ATM网络技术研修员</x:v>
+      </x:c>
+      <x:c r="D83" s="6" t="str">
+        <x:v>StrataCom公司</x:v>
+      </x:c>
+      <x:c r="E83" s="6" t="str">
+        <x:v>1996-02</x:v>
+      </x:c>
+      <x:c r="F83" s="6" t="str">
+        <x:v>1996-03</x:v>
+      </x:c>
+      <x:c r="G83" s="6" t="str"/>
+      <x:c r="H83" s="6" t="str"/>
+      <x:c r="I83" s="6" t="str"/>
+      <x:c r="J83" s="6" t="str"/>
+      <x:c r="K83" s="6" t="str"/>
+      <x:c r="L83" s="6" t="str"/>
+      <x:c r="M83" s="7" t="str"/>
+      <x:c r="N83" s="6" t="str"/>
+      <x:c r="O83" s="6" t="str"/>
+      <x:c r="P83" s="6" t="str"/>
+      <x:c r="Q83" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R83" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S83" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="64" customHeight="1">
+      <x:c r="A84" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B84" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C84" s="6" t="str">
+        <x:v>客座研究员</x:v>
+      </x:c>
+      <x:c r="D84" s="6" t="str">
+        <x:v>日本科学技术厅STA</x:v>
+      </x:c>
+      <x:c r="E84" s="6" t="str">
+        <x:v>1996-01</x:v>
+      </x:c>
+      <x:c r="F84" s="6" t="str">
+        <x:v>1996-02</x:v>
+      </x:c>
+      <x:c r="G84" s="6" t="str"/>
+      <x:c r="H84" s="6" t="str"/>
+      <x:c r="I84" s="6" t="str"/>
+      <x:c r="J84" s="6" t="str"/>
+      <x:c r="K84" s="6" t="str"/>
+      <x:c r="L84" s="6" t="str"/>
+      <x:c r="M84" s="7" t="str"/>
+      <x:c r="N84" s="6" t="str"/>
+      <x:c r="O84" s="6" t="str"/>
+      <x:c r="P84" s="6" t="str"/>
+      <x:c r="Q84" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R84" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S84" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="64" customHeight="1">
+      <x:c r="A85" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B85" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C85" s="6" t="str">
+        <x:v>客座研究员</x:v>
+      </x:c>
+      <x:c r="D85" s="6" t="str">
+        <x:v>日本通信振兴协会TAO</x:v>
+      </x:c>
+      <x:c r="E85" s="6" t="str">
+        <x:v>1995-10</x:v>
+      </x:c>
+      <x:c r="F85" s="6" t="str">
+        <x:v>1996-01</x:v>
+      </x:c>
+      <x:c r="G85" s="6" t="str"/>
+      <x:c r="H85" s="6" t="str"/>
+      <x:c r="I85" s="6" t="str"/>
+      <x:c r="J85" s="6" t="str"/>
+      <x:c r="K85" s="6" t="str"/>
+      <x:c r="L85" s="6" t="str"/>
+      <x:c r="M85" s="7" t="str"/>
+      <x:c r="N85" s="6" t="str"/>
+      <x:c r="O85" s="6" t="str"/>
+      <x:c r="P85" s="6" t="str"/>
+      <x:c r="Q85" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R85" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S85" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="64" customHeight="1">
+      <x:c r="A86" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B86" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C86" s="6" t="str">
+        <x:v>客座研究员</x:v>
+      </x:c>
+      <x:c r="D86" s="6" t="str">
+        <x:v>日本邮政省通信综合研究所CRL</x:v>
+      </x:c>
+      <x:c r="E86" s="6" t="str">
+        <x:v>1995-10</x:v>
+      </x:c>
+      <x:c r="F86" s="6" t="str">
+        <x:v>1996-02</x:v>
+      </x:c>
+      <x:c r="G86" s="6" t="str"/>
+      <x:c r="H86" s="6" t="str"/>
+      <x:c r="I86" s="6" t="str"/>
+      <x:c r="J86" s="6" t="str"/>
+      <x:c r="K86" s="6" t="str"/>
+      <x:c r="L86" s="6" t="str"/>
+      <x:c r="M86" s="7" t="str"/>
+      <x:c r="N86" s="6" t="str"/>
+      <x:c r="O86" s="6" t="str"/>
+      <x:c r="P86" s="6" t="str"/>
+      <x:c r="Q86" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R86" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S86" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f89b2f7f2542e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b1c04c1129419e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2701,7 +4760,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra24339e4430f4afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6efa73d828643ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3232,10 +5291,328 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Restricted Isometry Property of Subspace Projection Matrix Under Random Compression</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str"/>
+      <x:c r="E15" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J15" s="6" t="str"/>
+      <x:c r="K15" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L15" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>The Convergence Guarantees of a Non-convex Approach for Sparse Recovery</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str"/>
+      <x:c r="E16" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J16" s="6" t="str"/>
+      <x:c r="K16" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="64" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>Maximum Likelihood Estimation from Sign Measurements with Sensing Matrix Perturbation</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str"/>
+      <x:c r="E17" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L17" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>Predicting the Energy Landscape of Stochastic Dynamical System via Physics-informed Self-supervised Learning</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str"/>
+      <x:c r="E18" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J18" s="6" t="str">
+        <x:v>实验室清单明确署名Yong Li，精选非全集。</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="64" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>AgentSquare: Automatic LLM Agent Search in Modular Design Space</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str"/>
+      <x:c r="E19" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J19" s="6" t="str">
+        <x:v>实验室清单明确署名Yong Li，精选非全集。</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="64" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Symbolic regression via MDLformer-guided search: from minimizing prediction error to minimizing description length</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str"/>
+      <x:c r="E20" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J20" s="6" t="str">
+        <x:v>实验室清单明确署名Yong Li，精选非全集。</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="64" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>A UoI-Optimal Policy for Timely Status Updates with Resource Constraint</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str"/>
+      <x:c r="E21" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I21" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J21" s="6" t="str">
+        <x:v>官网精选书目，无逐篇出版者URL核定。</x:v>
+      </x:c>
+      <x:c r="K21" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="64" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Age-Optimal Scheduling for Heterogeneous Traffic With Timely Throughput Constraints</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str"/>
+      <x:c r="E22" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I22" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J22" s="6" t="str">
+        <x:v>官网精选书目，无逐篇出版者URL核定。</x:v>
+      </x:c>
+      <x:c r="K22" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L22" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Distributed Task Replication for Vehicular Edge Computing: Performance Analysis and Learning-Based Algorithm</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str"/>
+      <x:c r="E23" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I23" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J23" s="6" t="str">
+        <x:v>官网精选书目，无逐篇出版者URL核定。</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L23" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cfe147cada94485"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27f4d0287fdb4225"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4037,16 +6414,16 @@
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
-        <x:v>陈巍</x:v>
+        <x:v>谷源涛</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>guyuantao-source-1</x:v>
       </x:c>
       <x:c r="C35" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
       </x:c>
       <x:c r="D35" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E35" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4060,16 +6437,16 @@
     </x:row>
     <x:row r="36" ht="64" customHeight="1">
       <x:c r="A36" s="6" t="str">
-        <x:v>陈巍</x:v>
+        <x:v>谷源涛</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>guyuantao-source-2</x:v>
       </x:c>
       <x:c r="C36" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_personal_profile_body_read</x:v>
       </x:c>
       <x:c r="E36" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4083,16 +6460,16 @@
     </x:row>
     <x:row r="37" ht="64" customHeight="1">
       <x:c r="A37" s="6" t="str">
-        <x:v>戴凌龙</x:v>
+        <x:v>谷源涛</x:v>
       </x:c>
       <x:c r="B37" s="6" t="str">
-        <x:v>institution-classification-13</x:v>
+        <x:v>guyuantao-source-3</x:v>
       </x:c>
       <x:c r="C37" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/en/index.htm</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E37" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4106,16 +6483,16 @@
     </x:row>
     <x:row r="38" ht="64" customHeight="1">
       <x:c r="A38" s="6" t="str">
-        <x:v>戴凌龙</x:v>
+        <x:v>谷源涛</x:v>
       </x:c>
       <x:c r="B38" s="6" t="str">
-        <x:v>institution-classification-14</x:v>
+        <x:v>guyuantao-source-4</x:v>
       </x:c>
       <x:c r="C38" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://news.uestc.edu.cn/info/1009/15036.htm</x:v>
       </x:c>
       <x:c r="D38" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E38" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4129,16 +6506,16 @@
     </x:row>
     <x:row r="39" ht="64" customHeight="1">
       <x:c r="A39" s="6" t="str">
-        <x:v>樊平毅</x:v>
+        <x:v>谷源涛</x:v>
       </x:c>
       <x:c r="B39" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>guyuantao-source-5</x:v>
       </x:c>
       <x:c r="C39" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
       </x:c>
       <x:c r="D39" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E39" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4152,16 +6529,16 @@
     </x:row>
     <x:row r="40" ht="64" customHeight="1">
       <x:c r="A40" s="6" t="str">
-        <x:v>樊平毅</x:v>
+        <x:v>李勇</x:v>
       </x:c>
       <x:c r="B40" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>liyong-source-1</x:v>
       </x:c>
       <x:c r="C40" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
       </x:c>
       <x:c r="D40" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E40" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4175,16 +6552,16 @@
     </x:row>
     <x:row r="41" ht="64" customHeight="1">
       <x:c r="A41" s="6" t="str">
-        <x:v>冯伟</x:v>
+        <x:v>李勇</x:v>
       </x:c>
       <x:c r="B41" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>liyong-source-2</x:v>
       </x:c>
       <x:c r="C41" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D41" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_personal_profile_body_read</x:v>
       </x:c>
       <x:c r="E41" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4198,16 +6575,16 @@
     </x:row>
     <x:row r="42" ht="64" customHeight="1">
       <x:c r="A42" s="6" t="str">
-        <x:v>葛宁</x:v>
+        <x:v>李勇</x:v>
       </x:c>
       <x:c r="B42" s="6" t="str">
-        <x:v>institution-classification-7</x:v>
+        <x:v>liyong-source-3</x:v>
       </x:c>
       <x:c r="C42" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://fi.ee.tsinghua.edu.cn/~liyong/</x:v>
       </x:c>
       <x:c r="D42" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E42" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -4221,31 +6598,606 @@
     </x:row>
     <x:row r="43" ht="64" customHeight="1">
       <x:c r="A43" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>liyong-source-4</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="64" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>lujianhua-source-1</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="64" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>lujianhua-source-2</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/lujianhua/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>official_personal_profile_body_read</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>lujianhua-source-3</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>suxin-source-1</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="64" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>suxin-source-2</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/suxin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>official_personal_profile_body_read</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="64" customHeight="1">
+      <x:c r="A49" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>suxin-source-3</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="str">
+        <x:v>https://physics.swu.edu.cn/info/1077/2131.htm</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F49" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="64" customHeight="1">
+      <x:c r="A50" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>niuzhisheng-source-1</x:v>
+      </x:c>
+      <x:c r="C50" s="6" t="str">
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="64" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>niuzhisheng-source-2</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>official_personal_profile_body_read</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F51" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" s="6" t="str">
+        <x:v>牛志升</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>niuzhisheng-source-3</x:v>
+      </x:c>
+      <x:c r="C52" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F52" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" s="6" t="str">
+        <x:v>陈巍</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C53" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F53" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" s="6" t="str">
+        <x:v>陈巍</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C54" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F54" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" s="6" t="str">
+        <x:v>戴凌龙</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>institution-classification-13</x:v>
+      </x:c>
+      <x:c r="C55" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F55" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="64" customHeight="1">
+      <x:c r="A56" s="6" t="str">
+        <x:v>戴凌龙</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>institution-classification-14</x:v>
+      </x:c>
+      <x:c r="C56" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D56" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F56" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G56" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="64" customHeight="1">
+      <x:c r="A57" s="6" t="str">
+        <x:v>樊平毅</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C57" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D57" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F57" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="64" customHeight="1">
+      <x:c r="A58" s="6" t="str">
+        <x:v>樊平毅</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C58" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D58" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="64" customHeight="1">
+      <x:c r="A59" s="6" t="str">
+        <x:v>冯伟</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C59" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D59" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F59" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="64" customHeight="1">
+      <x:c r="A60" s="6" t="str">
         <x:v>葛宁</x:v>
       </x:c>
-      <x:c r="B43" s="6" t="str">
+      <x:c r="B60" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C60" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D60" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F60" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="64" customHeight="1">
+      <x:c r="A61" s="6" t="str">
+        <x:v>葛宁</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
         <x:v>institution-classification-8</x:v>
       </x:c>
-      <x:c r="C43" s="6" t="str">
+      <x:c r="C61" s="6" t="str">
         <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
       </x:c>
-      <x:c r="D43" s="6" t="str">
+      <x:c r="D61" s="6" t="str">
         <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
       </x:c>
-      <x:c r="E43" s="7" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F43" s="6" t="str">
-        <x:v>thu</x:v>
-      </x:c>
-      <x:c r="G43" s="6" t="str">
+      <x:c r="E61" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F61" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="64" customHeight="1">
+      <x:c r="A62" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C62" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D62" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F62" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G62" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="64" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D63" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F63" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G63" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="64" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C64" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D64" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F64" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G64" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="64" customHeight="1">
+      <x:c r="A65" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C65" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D65" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F65" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G65" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="64" customHeight="1">
+      <x:c r="A66" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C66" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D66" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E66" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F66" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G66" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="64" customHeight="1">
+      <x:c r="A67" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C67" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D67" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F67" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G67" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="64" customHeight="1">
+      <x:c r="A68" s="6" t="str">
+        <x:v>粟欣</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C68" s="6" t="str">
+        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+      </x:c>
+      <x:c r="D68" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F68" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str">
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfad1125e34e840ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ad9b20f2a3d41e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/thu-ee-communications.xlsx
+++ b/site/exports/thu-ee-communications.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R57238adf11584adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R461c4c3f8af94f4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R64924e7bdb7c4d77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R4e563b732f0046df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rdf638849327c4c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf13c36126e814830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Ra913753b3b7140f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rfb918ca988b84739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rc7fed85c4a884d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R8153de0dc7a440fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T9_0" displayName="T9_0" ref="A1:K11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T9_0" displayName="T9_0" ref="A1:K16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T9_1" displayName="T9_1" ref="A1:S86" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T9_1" displayName="T9_1" ref="A1:S121" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T9_2" displayName="T9_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T9_2" displayName="T9_2" ref="A1:L4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T9_3" displayName="T9_3" ref="A1:L23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T9_3" displayName="T9_3" ref="A1:L28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T9_4" displayName="T9_4" ref="A1:G68" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T9_4" displayName="T9_4" ref="A1:G89" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -812,10 +812,175 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>清华头部2009.12入职与简介2011留校对应博士后/后续岗位，不简单视为同一任职事件。；教授起始时间两校官网2018.12/2020.08不同，明确保留，不据选择消除冲突。；博士后导师未核，不能把博士导师自动延伸到博士后。</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjingtao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>未核各阶段导师；官网学术论文栏目为空时不等于没有论文。</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>学位年月及导师未知；与哈工大威海等同名王军分开，清华官方身份独立。；官网学术论文共0条，仅栏目未填，不宣称无成果。</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>未核各阶段导师；官网学术论文栏目为空时不等于没有论文。</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str"/>
+      <x:c r="J15" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="64" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>电子工程系·通信研究所</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>学位年月与各阶段导师未核；头部副书记未说明组织及当前任期，不作为精确行政职务。；本人学术论文栏目共0条，不等于无论文。</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racbb202377704da8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e71ff1cd72048f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4621,10 +4786,1505 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="87" ht="64" customHeight="1">
+      <x:c r="A87" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B87" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C87" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D87" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E87" s="6" t="str">
+        <x:v>1999-09</x:v>
+      </x:c>
+      <x:c r="F87" s="6" t="str">
+        <x:v>2003-06</x:v>
+      </x:c>
+      <x:c r="G87" s="6" t="str">
+        <x:v>通信工程</x:v>
+      </x:c>
+      <x:c r="H87" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I87" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J87" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K87" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L87" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M87" s="7" t="str"/>
+      <x:c r="N87" s="6" t="str"/>
+      <x:c r="O87" s="6" t="str"/>
+      <x:c r="P87" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q87" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R87" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S87" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="64" customHeight="1">
+      <x:c r="A88" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B88" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C88" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D88" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E88" s="6" t="str">
+        <x:v>2003-09</x:v>
+      </x:c>
+      <x:c r="F88" s="6" t="str">
+        <x:v>2008-06</x:v>
+      </x:c>
+      <x:c r="G88" s="6" t="str">
+        <x:v>信息与通信系统</x:v>
+      </x:c>
+      <x:c r="H88" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I88" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J88" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K88" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L88" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M88" s="7" t="str"/>
+      <x:c r="N88" s="6" t="str"/>
+      <x:c r="O88" s="6" t="str">
+        <x:v>本人教育专业原文；学位论文题录学科名为信息与通信工程，保留不同字段口径，不把答辩2008-06-06作为授位日。</x:v>
+      </x:c>
+      <x:c r="P88" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q88" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R88" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S88" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="64" customHeight="1">
+      <x:c r="A89" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B89" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C89" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D89" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E89" s="6" t="str"/>
+      <x:c r="F89" s="6" t="str"/>
+      <x:c r="G89" s="6" t="str"/>
+      <x:c r="H89" s="6" t="str"/>
+      <x:c r="I89" s="6" t="str"/>
+      <x:c r="J89" s="6" t="str"/>
+      <x:c r="K89" s="6" t="str"/>
+      <x:c r="L89" s="6" t="str"/>
+      <x:c r="M89" s="7" t="str"/>
+      <x:c r="N89" s="6" t="str"/>
+      <x:c r="O89" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P89" s="6" t="str"/>
+      <x:c r="Q89" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R89" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S89" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="64" customHeight="1">
+      <x:c r="A90" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B90" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C90" s="6" t="str">
+        <x:v>Researcher</x:v>
+      </x:c>
+      <x:c r="D90" s="6" t="str">
+        <x:v>法国电信集团Orange Labs</x:v>
+      </x:c>
+      <x:c r="E90" s="6" t="str">
+        <x:v>2008-07</x:v>
+      </x:c>
+      <x:c r="F90" s="6" t="str">
+        <x:v>2009-12</x:v>
+      </x:c>
+      <x:c r="G90" s="6" t="str"/>
+      <x:c r="H90" s="6" t="str"/>
+      <x:c r="I90" s="6" t="str"/>
+      <x:c r="J90" s="6" t="str"/>
+      <x:c r="K90" s="6" t="str"/>
+      <x:c r="L90" s="6" t="str"/>
+      <x:c r="M90" s="7" t="str"/>
+      <x:c r="N90" s="6" t="str"/>
+      <x:c r="O90" s="6" t="str"/>
+      <x:c r="P90" s="6" t="str"/>
+      <x:c r="Q90" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="R90" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S90" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="64" customHeight="1">
+      <x:c r="A91" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B91" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C91" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D91" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E91" s="6" t="str">
+        <x:v>2009-12</x:v>
+      </x:c>
+      <x:c r="F91" s="6" t="str">
+        <x:v>2011-11</x:v>
+      </x:c>
+      <x:c r="G91" s="6" t="str"/>
+      <x:c r="H91" s="6" t="str"/>
+      <x:c r="I91" s="6" t="str"/>
+      <x:c r="J91" s="6" t="str"/>
+      <x:c r="K91" s="6" t="str"/>
+      <x:c r="L91" s="6" t="str"/>
+      <x:c r="M91" s="7" t="str"/>
+      <x:c r="N91" s="6" t="str"/>
+      <x:c r="O91" s="6" t="str"/>
+      <x:c r="P91" s="6" t="str"/>
+      <x:c r="Q91" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="R91" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S91" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="64" customHeight="1">
+      <x:c r="A92" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B92" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C92" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D92" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E92" s="6" t="str">
+        <x:v>2011-12</x:v>
+      </x:c>
+      <x:c r="F92" s="6" t="str">
+        <x:v>2014-11</x:v>
+      </x:c>
+      <x:c r="G92" s="6" t="str"/>
+      <x:c r="H92" s="6" t="str"/>
+      <x:c r="I92" s="6" t="str"/>
+      <x:c r="J92" s="6" t="str"/>
+      <x:c r="K92" s="6" t="str"/>
+      <x:c r="L92" s="6" t="str"/>
+      <x:c r="M92" s="7" t="str"/>
+      <x:c r="N92" s="6" t="str"/>
+      <x:c r="O92" s="6" t="str"/>
+      <x:c r="P92" s="6" t="str"/>
+      <x:c r="Q92" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="R92" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S92" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="64" customHeight="1">
+      <x:c r="A93" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B93" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C93" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D93" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E93" s="6" t="str">
+        <x:v>2014-12</x:v>
+      </x:c>
+      <x:c r="F93" s="6" t="str">
+        <x:v>2018-11</x:v>
+      </x:c>
+      <x:c r="G93" s="6" t="str"/>
+      <x:c r="H93" s="6" t="str"/>
+      <x:c r="I93" s="6" t="str"/>
+      <x:c r="J93" s="6" t="str"/>
+      <x:c r="K93" s="6" t="str"/>
+      <x:c r="L93" s="6" t="str"/>
+      <x:c r="M93" s="7" t="str"/>
+      <x:c r="N93" s="6" t="str"/>
+      <x:c r="O93" s="6" t="str"/>
+      <x:c r="P93" s="6" t="str"/>
+      <x:c r="Q93" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="R93" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S93" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="64" customHeight="1">
+      <x:c r="A94" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B94" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C94" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D94" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E94" s="6" t="str">
+        <x:v>2018-12</x:v>
+      </x:c>
+      <x:c r="F94" s="6" t="str">
+        <x:v>2020-07</x:v>
+      </x:c>
+      <x:c r="G94" s="6" t="str"/>
+      <x:c r="H94" s="6" t="str"/>
+      <x:c r="I94" s="6" t="str"/>
+      <x:c r="J94" s="6" t="str"/>
+      <x:c r="K94" s="6" t="str"/>
+      <x:c r="L94" s="6" t="str"/>
+      <x:c r="M94" s="7" t="str"/>
+      <x:c r="N94" s="6" t="str"/>
+      <x:c r="O94" s="6" t="str">
+        <x:v>清华本人页如此列，另一新疆大学本人履历称2018.12起教授，有职称口径冲突。</x:v>
+      </x:c>
+      <x:c r="P94" s="6" t="str"/>
+      <x:c r="Q94" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R94" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S94" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="64" customHeight="1">
+      <x:c r="A95" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B95" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C95" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D95" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E95" s="6" t="str">
+        <x:v>2020-08</x:v>
+      </x:c>
+      <x:c r="F95" s="6" t="str"/>
+      <x:c r="G95" s="6" t="str"/>
+      <x:c r="H95" s="6" t="str"/>
+      <x:c r="I95" s="6" t="str"/>
+      <x:c r="J95" s="6" t="str"/>
+      <x:c r="K95" s="6" t="str"/>
+      <x:c r="L95" s="6" t="str"/>
+      <x:c r="M95" s="7" t="str"/>
+      <x:c r="N95" s="6" t="str"/>
+      <x:c r="O95" s="6" t="str">
+        <x:v>本人清华页起始2020.08，新疆大学页2018.12，不能确定无争议教授聘任月。</x:v>
+      </x:c>
+      <x:c r="P95" s="6" t="str"/>
+      <x:c r="Q95" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R95" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S95" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="64" customHeight="1">
+      <x:c r="A96" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B96" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C96" s="6" t="str">
+        <x:v>院长、教授</x:v>
+      </x:c>
+      <x:c r="D96" s="6" t="str">
+        <x:v>新疆大学计算机科学与技术学院</x:v>
+      </x:c>
+      <x:c r="E96" s="6" t="str">
+        <x:v>2024-11</x:v>
+      </x:c>
+      <x:c r="F96" s="6" t="str"/>
+      <x:c r="G96" s="6" t="str"/>
+      <x:c r="H96" s="6" t="str"/>
+      <x:c r="I96" s="6" t="str"/>
+      <x:c r="J96" s="6" t="str"/>
+      <x:c r="K96" s="6" t="str"/>
+      <x:c r="L96" s="6" t="str"/>
+      <x:c r="M96" s="7" t="str"/>
+      <x:c r="N96" s="6" t="str"/>
+      <x:c r="O96" s="6" t="str">
+        <x:v>两校本人页同时列示，保留双归属，不推辞去清华职位。</x:v>
+      </x:c>
+      <x:c r="P96" s="6" t="str"/>
+      <x:c r="Q96" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="R96" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S96" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="64" customHeight="1">
+      <x:c r="A97" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B97" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C97" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D97" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E97" s="6" t="str"/>
+      <x:c r="F97" s="6" t="str">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="G97" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H97" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I97" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J97" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K97" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L97" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M97" s="7" t="str"/>
+      <x:c r="N97" s="6" t="str"/>
+      <x:c r="O97" s="6" t="str"/>
+      <x:c r="P97" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q97" s="6" t="str">
+        <x:v>https://vtsociety.org/contact/jintao-wang</x:v>
+      </x:c>
+      <x:c r="R97" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S97" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="64" customHeight="1">
+      <x:c r="A98" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B98" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C98" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D98" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E98" s="6" t="str"/>
+      <x:c r="F98" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="G98" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H98" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I98" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J98" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K98" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L98" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M98" s="7" t="str"/>
+      <x:c r="N98" s="6" t="str"/>
+      <x:c r="O98" s="6" t="str"/>
+      <x:c r="P98" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q98" s="6" t="str">
+        <x:v>https://vtsociety.org/contact/jintao-wang</x:v>
+      </x:c>
+      <x:c r="R98" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S98" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="64" customHeight="1">
+      <x:c r="A99" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B99" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C99" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D99" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E99" s="6" t="str"/>
+      <x:c r="F99" s="6" t="str"/>
+      <x:c r="G99" s="6" t="str"/>
+      <x:c r="H99" s="6" t="str"/>
+      <x:c r="I99" s="6" t="str"/>
+      <x:c r="J99" s="6" t="str"/>
+      <x:c r="K99" s="6" t="str"/>
+      <x:c r="L99" s="6" t="str"/>
+      <x:c r="M99" s="7" t="str"/>
+      <x:c r="N99" s="6" t="str"/>
+      <x:c r="O99" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P99" s="6" t="str"/>
+      <x:c r="Q99" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjingtao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R99" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S99" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="64" customHeight="1">
+      <x:c r="A100" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B100" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C100" s="6" t="str">
+        <x:v>任教（分职级起讫未核）</x:v>
+      </x:c>
+      <x:c r="D100" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E100" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="F100" s="6" t="str"/>
+      <x:c r="G100" s="6" t="str"/>
+      <x:c r="H100" s="6" t="str"/>
+      <x:c r="I100" s="6" t="str"/>
+      <x:c r="J100" s="6" t="str"/>
+      <x:c r="K100" s="6" t="str"/>
+      <x:c r="L100" s="6" t="str"/>
+      <x:c r="M100" s="7" t="str"/>
+      <x:c r="N100" s="6" t="str"/>
+      <x:c r="O100" s="6" t="str"/>
+      <x:c r="P100" s="6" t="str"/>
+      <x:c r="Q100" s="6" t="str">
+        <x:v>https://vtsociety.org/contact/jintao-wang</x:v>
+      </x:c>
+      <x:c r="R100" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S100" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="64" customHeight="1">
+      <x:c r="A101" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B101" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C101" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D101" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E101" s="6" t="str"/>
+      <x:c r="F101" s="6" t="str"/>
+      <x:c r="G101" s="6" t="str">
+        <x:v>电子工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H101" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I101" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J101" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K101" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L101" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M101" s="7" t="str"/>
+      <x:c r="N101" s="6" t="str"/>
+      <x:c r="O101" s="6" t="str"/>
+      <x:c r="P101" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q101" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R101" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S101" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="64" customHeight="1">
+      <x:c r="A102" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B102" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C102" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D102" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E102" s="6" t="str"/>
+      <x:c r="F102" s="6" t="str"/>
+      <x:c r="G102" s="6" t="str">
+        <x:v>电子工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H102" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I102" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J102" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K102" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L102" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M102" s="7" t="str"/>
+      <x:c r="N102" s="6" t="str"/>
+      <x:c r="O102" s="6" t="str"/>
+      <x:c r="P102" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q102" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R102" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S102" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="64" customHeight="1">
+      <x:c r="A103" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B103" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C103" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D103" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E103" s="6" t="str"/>
+      <x:c r="F103" s="6" t="str"/>
+      <x:c r="G103" s="6" t="str"/>
+      <x:c r="H103" s="6" t="str"/>
+      <x:c r="I103" s="6" t="str"/>
+      <x:c r="J103" s="6" t="str"/>
+      <x:c r="K103" s="6" t="str"/>
+      <x:c r="L103" s="6" t="str"/>
+      <x:c r="M103" s="7" t="str"/>
+      <x:c r="N103" s="6" t="str"/>
+      <x:c r="O103" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P103" s="6" t="str"/>
+      <x:c r="Q103" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R103" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S103" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="64" customHeight="1">
+      <x:c r="A104" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B104" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C104" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D104" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E104" s="6" t="str">
+        <x:v>2004-03</x:v>
+      </x:c>
+      <x:c r="F104" s="6" t="str">
+        <x:v>2007-12</x:v>
+      </x:c>
+      <x:c r="G104" s="6" t="str"/>
+      <x:c r="H104" s="6" t="str"/>
+      <x:c r="I104" s="6" t="str"/>
+      <x:c r="J104" s="6" t="str"/>
+      <x:c r="K104" s="6" t="str"/>
+      <x:c r="L104" s="6" t="str"/>
+      <x:c r="M104" s="7" t="str"/>
+      <x:c r="N104" s="6" t="str"/>
+      <x:c r="O104" s="6" t="str"/>
+      <x:c r="P104" s="6" t="str"/>
+      <x:c r="Q104" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R104" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S104" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="64" customHeight="1">
+      <x:c r="A105" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B105" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C105" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D105" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E105" s="6" t="str">
+        <x:v>2007-12</x:v>
+      </x:c>
+      <x:c r="F105" s="6" t="str">
+        <x:v>2017-12</x:v>
+      </x:c>
+      <x:c r="G105" s="6" t="str"/>
+      <x:c r="H105" s="6" t="str"/>
+      <x:c r="I105" s="6" t="str"/>
+      <x:c r="J105" s="6" t="str"/>
+      <x:c r="K105" s="6" t="str"/>
+      <x:c r="L105" s="6" t="str"/>
+      <x:c r="M105" s="7" t="str"/>
+      <x:c r="N105" s="6" t="str"/>
+      <x:c r="O105" s="6" t="str"/>
+      <x:c r="P105" s="6" t="str"/>
+      <x:c r="Q105" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R105" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S105" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="64" customHeight="1">
+      <x:c r="A106" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B106" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C106" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D106" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E106" s="6" t="str">
+        <x:v>2017-12</x:v>
+      </x:c>
+      <x:c r="F106" s="6" t="str"/>
+      <x:c r="G106" s="6" t="str"/>
+      <x:c r="H106" s="6" t="str"/>
+      <x:c r="I106" s="6" t="str"/>
+      <x:c r="J106" s="6" t="str"/>
+      <x:c r="K106" s="6" t="str"/>
+      <x:c r="L106" s="6" t="str"/>
+      <x:c r="M106" s="7" t="str"/>
+      <x:c r="N106" s="6" t="str"/>
+      <x:c r="O106" s="6" t="str"/>
+      <x:c r="P106" s="6" t="str"/>
+      <x:c r="Q106" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R106" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S106" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="64" customHeight="1">
+      <x:c r="A107" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B107" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C107" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D107" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E107" s="6" t="str">
+        <x:v>1986-09</x:v>
+      </x:c>
+      <x:c r="F107" s="6" t="str">
+        <x:v>1991-07</x:v>
+      </x:c>
+      <x:c r="G107" s="6" t="str">
+        <x:v>无线电电子学系（院系）</x:v>
+      </x:c>
+      <x:c r="H107" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I107" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J107" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K107" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L107" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M107" s="7" t="str"/>
+      <x:c r="N107" s="6" t="str"/>
+      <x:c r="O107" s="6" t="str"/>
+      <x:c r="P107" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q107" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R107" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S107" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="64" customHeight="1">
+      <x:c r="A108" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B108" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C108" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D108" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E108" s="6" t="str">
+        <x:v>1991-09</x:v>
+      </x:c>
+      <x:c r="F108" s="6" t="str">
+        <x:v>1993-07</x:v>
+      </x:c>
+      <x:c r="G108" s="6" t="str">
+        <x:v>电子工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H108" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I108" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J108" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K108" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L108" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M108" s="7" t="str"/>
+      <x:c r="N108" s="6" t="str"/>
+      <x:c r="O108" s="6" t="str"/>
+      <x:c r="P108" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q108" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R108" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S108" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="64" customHeight="1">
+      <x:c r="A109" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B109" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C109" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D109" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E109" s="6" t="str">
+        <x:v>1993-09</x:v>
+      </x:c>
+      <x:c r="F109" s="6" t="str">
+        <x:v>1996-07</x:v>
+      </x:c>
+      <x:c r="G109" s="6" t="str">
+        <x:v>电子工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H109" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I109" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J109" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K109" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L109" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M109" s="7" t="str"/>
+      <x:c r="N109" s="6" t="str"/>
+      <x:c r="O109" s="6" t="str"/>
+      <x:c r="P109" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q109" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R109" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S109" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="64" customHeight="1">
+      <x:c r="A110" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B110" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C110" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D110" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E110" s="6" t="str"/>
+      <x:c r="F110" s="6" t="str"/>
+      <x:c r="G110" s="6" t="str"/>
+      <x:c r="H110" s="6" t="str"/>
+      <x:c r="I110" s="6" t="str"/>
+      <x:c r="J110" s="6" t="str"/>
+      <x:c r="K110" s="6" t="str"/>
+      <x:c r="L110" s="6" t="str"/>
+      <x:c r="M110" s="7" t="str"/>
+      <x:c r="N110" s="6" t="str"/>
+      <x:c r="O110" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P110" s="6" t="str"/>
+      <x:c r="Q110" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R110" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S110" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="64" customHeight="1">
+      <x:c r="A111" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B111" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C111" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D111" s="6" t="str">
+        <x:v>南洋理工大学</x:v>
+      </x:c>
+      <x:c r="E111" s="6" t="str">
+        <x:v>1996-10</x:v>
+      </x:c>
+      <x:c r="F111" s="6" t="str">
+        <x:v>1997-09</x:v>
+      </x:c>
+      <x:c r="G111" s="6" t="str"/>
+      <x:c r="H111" s="6" t="str"/>
+      <x:c r="I111" s="6" t="str"/>
+      <x:c r="J111" s="6" t="str"/>
+      <x:c r="K111" s="6" t="str"/>
+      <x:c r="L111" s="6" t="str"/>
+      <x:c r="M111" s="7" t="str"/>
+      <x:c r="N111" s="6" t="str"/>
+      <x:c r="O111" s="6" t="str"/>
+      <x:c r="P111" s="6" t="str"/>
+      <x:c r="Q111" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R111" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S111" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="64" customHeight="1">
+      <x:c r="A112" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B112" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C112" s="6" t="str">
+        <x:v>研发工程师/高级工程师</x:v>
+      </x:c>
+      <x:c r="D112" s="6" t="str">
+        <x:v>OKI技术中心（新加坡）</x:v>
+      </x:c>
+      <x:c r="E112" s="6" t="str">
+        <x:v>1997-10</x:v>
+      </x:c>
+      <x:c r="F112" s="6" t="str">
+        <x:v>1999-09</x:v>
+      </x:c>
+      <x:c r="G112" s="6" t="str"/>
+      <x:c r="H112" s="6" t="str"/>
+      <x:c r="I112" s="6" t="str"/>
+      <x:c r="J112" s="6" t="str"/>
+      <x:c r="K112" s="6" t="str"/>
+      <x:c r="L112" s="6" t="str"/>
+      <x:c r="M112" s="7" t="str"/>
+      <x:c r="N112" s="6" t="str"/>
+      <x:c r="O112" s="6" t="str"/>
+      <x:c r="P112" s="6" t="str"/>
+      <x:c r="Q112" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R112" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S112" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="64" customHeight="1">
+      <x:c r="A113" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B113" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C113" s="6" t="str">
+        <x:v>高级工程师/主任工程师</x:v>
+      </x:c>
+      <x:c r="D113" s="6" t="str">
+        <x:v>SONY欧洲研发中心（德国）</x:v>
+      </x:c>
+      <x:c r="E113" s="6" t="str">
+        <x:v>1999-09</x:v>
+      </x:c>
+      <x:c r="F113" s="6" t="str">
+        <x:v>2009-04</x:v>
+      </x:c>
+      <x:c r="G113" s="6" t="str"/>
+      <x:c r="H113" s="6" t="str"/>
+      <x:c r="I113" s="6" t="str"/>
+      <x:c r="J113" s="6" t="str"/>
+      <x:c r="K113" s="6" t="str"/>
+      <x:c r="L113" s="6" t="str"/>
+      <x:c r="M113" s="7" t="str"/>
+      <x:c r="N113" s="6" t="str"/>
+      <x:c r="O113" s="6" t="str"/>
+      <x:c r="P113" s="6" t="str"/>
+      <x:c r="Q113" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R113" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S113" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="64" customHeight="1">
+      <x:c r="A114" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B114" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C114" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D114" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E114" s="6" t="str">
+        <x:v>2009-04</x:v>
+      </x:c>
+      <x:c r="F114" s="6" t="str"/>
+      <x:c r="G114" s="6" t="str"/>
+      <x:c r="H114" s="6" t="str"/>
+      <x:c r="I114" s="6" t="str"/>
+      <x:c r="J114" s="6" t="str"/>
+      <x:c r="K114" s="6" t="str"/>
+      <x:c r="L114" s="6" t="str"/>
+      <x:c r="M114" s="7" t="str"/>
+      <x:c r="N114" s="6" t="str"/>
+      <x:c r="O114" s="6" t="str"/>
+      <x:c r="P114" s="6" t="str"/>
+      <x:c r="Q114" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R114" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S114" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="64" customHeight="1">
+      <x:c r="A115" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B115" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C115" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D115" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+      <x:c r="E115" s="6" t="str"/>
+      <x:c r="F115" s="6" t="str"/>
+      <x:c r="G115" s="6" t="str">
+        <x:v>无线电工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H115" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I115" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J115" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K115" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L115" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M115" s="7" t="str"/>
+      <x:c r="N115" s="6" t="str"/>
+      <x:c r="O115" s="6" t="str"/>
+      <x:c r="P115" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q115" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R115" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S115" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="64" customHeight="1">
+      <x:c r="A116" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B116" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C116" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D116" s="6" t="str">
+        <x:v>东南大学</x:v>
+      </x:c>
+      <x:c r="E116" s="6" t="str"/>
+      <x:c r="F116" s="6" t="str"/>
+      <x:c r="G116" s="6" t="str">
+        <x:v>无线电工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H116" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I116" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J116" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K116" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L116" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M116" s="7" t="str"/>
+      <x:c r="N116" s="6" t="str"/>
+      <x:c r="O116" s="6" t="str"/>
+      <x:c r="P116" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q116" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R116" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S116" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="64" customHeight="1">
+      <x:c r="A117" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B117" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C117" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D117" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+      <x:c r="E117" s="6" t="str"/>
+      <x:c r="F117" s="6" t="str"/>
+      <x:c r="G117" s="6" t="str">
+        <x:v>电子工程系（院系）</x:v>
+      </x:c>
+      <x:c r="H117" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I117" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J117" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K117" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L117" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M117" s="7" t="str"/>
+      <x:c r="N117" s="6" t="str"/>
+      <x:c r="O117" s="6" t="str"/>
+      <x:c r="P117" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q117" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R117" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S117" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="64" customHeight="1">
+      <x:c r="A118" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B118" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C118" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D118" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E118" s="6" t="str"/>
+      <x:c r="F118" s="6" t="str"/>
+      <x:c r="G118" s="6" t="str"/>
+      <x:c r="H118" s="6" t="str"/>
+      <x:c r="I118" s="6" t="str"/>
+      <x:c r="J118" s="6" t="str"/>
+      <x:c r="K118" s="6" t="str"/>
+      <x:c r="L118" s="6" t="str"/>
+      <x:c r="M118" s="7" t="str"/>
+      <x:c r="N118" s="6" t="str"/>
+      <x:c r="O118" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P118" s="6" t="str"/>
+      <x:c r="Q118" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R118" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S118" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="64" customHeight="1">
+      <x:c r="A119" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B119" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C119" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D119" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E119" s="6" t="str">
+        <x:v>1997-07</x:v>
+      </x:c>
+      <x:c r="F119" s="6" t="str">
+        <x:v>1999-12</x:v>
+      </x:c>
+      <x:c r="G119" s="6" t="str"/>
+      <x:c r="H119" s="6" t="str"/>
+      <x:c r="I119" s="6" t="str"/>
+      <x:c r="J119" s="6" t="str"/>
+      <x:c r="K119" s="6" t="str"/>
+      <x:c r="L119" s="6" t="str"/>
+      <x:c r="M119" s="7" t="str"/>
+      <x:c r="N119" s="6" t="str"/>
+      <x:c r="O119" s="6" t="str"/>
+      <x:c r="P119" s="6" t="str"/>
+      <x:c r="Q119" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R119" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S119" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="64" customHeight="1">
+      <x:c r="A120" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B120" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C120" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D120" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E120" s="6" t="str">
+        <x:v>1999-12</x:v>
+      </x:c>
+      <x:c r="F120" s="6" t="str">
+        <x:v>2004-12</x:v>
+      </x:c>
+      <x:c r="G120" s="6" t="str"/>
+      <x:c r="H120" s="6" t="str"/>
+      <x:c r="I120" s="6" t="str"/>
+      <x:c r="J120" s="6" t="str"/>
+      <x:c r="K120" s="6" t="str"/>
+      <x:c r="L120" s="6" t="str"/>
+      <x:c r="M120" s="7" t="str"/>
+      <x:c r="N120" s="6" t="str"/>
+      <x:c r="O120" s="6" t="str"/>
+      <x:c r="P120" s="6" t="str"/>
+      <x:c r="Q120" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R120" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S120" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="64" customHeight="1">
+      <x:c r="A121" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B121" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C121" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D121" s="6" t="str">
+        <x:v>清华大学电子工程系</x:v>
+      </x:c>
+      <x:c r="E121" s="6" t="str">
+        <x:v>2004-12</x:v>
+      </x:c>
+      <x:c r="F121" s="6" t="str"/>
+      <x:c r="G121" s="6" t="str"/>
+      <x:c r="H121" s="6" t="str"/>
+      <x:c r="I121" s="6" t="str"/>
+      <x:c r="J121" s="6" t="str"/>
+      <x:c r="K121" s="6" t="str"/>
+      <x:c r="L121" s="6" t="str"/>
+      <x:c r="M121" s="7" t="str"/>
+      <x:c r="N121" s="6" t="str"/>
+      <x:c r="O121" s="6" t="str"/>
+      <x:c r="P121" s="6" t="str"/>
+      <x:c r="Q121" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R121" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="S121" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32b1c04c1129419e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb6a2e509ef14d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4757,10 +6417,48 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>清华大学电子工程系教授、中国科学院院士，研究通信与信息系统。</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>active_officially_listed</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>清华院士页明确现为教授，仅官方列示，不独立人事核验。</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>https://newetds.lib.tsinghua.edu.cn/qh/paper/summary?dbCode=ETDQH&amp;sysId=173003</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6efa73d828643ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc55b8a2b674274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5609,10 +7307,194 @@
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>高速移动环境多载波传输关键技术研究</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str"/>
+      <x:c r="E24" s="6" t="str">
+        <x:v>https://newetds.lib.tsinghua.edu.cn/qh/paper/summary?dbCode=ETDQH&amp;sysId=173003</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>https://newetds.lib.tsinghua.edu.cn/qh/paper/summary?dbCode=ETDQH&amp;sysId=173003</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>公开题录，答辩2008-06-06；不公开全文或学生学号。</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>A multimodal physiological dataset for driving behaviour analysis</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str"/>
+      <x:c r="E25" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str">
+        <x:v>本人官网精选书目，未逐篇查出版者或补DOI。</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L25" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Brain-Inspired Image Perceptual Quality Assessment Based on EEG: A QoE Perspective</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str"/>
+      <x:c r="E26" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I26" s="6" t="str">
+        <x:v>official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J26" s="6" t="str">
+        <x:v>本人官网精选书目，未逐篇查出版者或补DOI。</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L26" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>Spectrum- and Energy-Efficient OFDM Based on Simultaneous Multi-Channel Reconstruction</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>10.1109/TSP.2013.2282920</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjingtao/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I27" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J27" s="6" t="str">
+        <x:v>清华作者官网论文副本首页署名与机构直接核，非从共同作者推导师。</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>Spectrum- and Energy-Efficient OFDM Based on Simultaneous Multi-Channel Reconstruction</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>10.1109/TSP.2013.2282920</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
+        <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I28" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J28" s="6" t="str">
+        <x:v>清华作者官网论文副本首页署名与机构直接核，非从共同作者推导师。</x:v>
+      </x:c>
+      <x:c r="K28" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="L28" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27f4d0287fdb4225"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bfd69f510024194"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6828,16 +8710,16 @@
     </x:row>
     <x:row r="53" ht="64" customHeight="1">
       <x:c r="A53" s="6" t="str">
-        <x:v>陈巍</x:v>
+        <x:v>陶晓明</x:v>
       </x:c>
       <x:c r="B53" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>taoxiaoming-source-1</x:v>
       </x:c>
       <x:c r="C53" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
       </x:c>
       <x:c r="D53" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E53" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6851,16 +8733,16 @@
     </x:row>
     <x:row r="54" ht="64" customHeight="1">
       <x:c r="A54" s="6" t="str">
-        <x:v>陈巍</x:v>
+        <x:v>陶晓明</x:v>
       </x:c>
       <x:c r="B54" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>taoxiaoming-source-2</x:v>
       </x:c>
       <x:c r="C54" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D54" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E54" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6874,16 +8756,16 @@
     </x:row>
     <x:row r="55" ht="64" customHeight="1">
       <x:c r="A55" s="6" t="str">
-        <x:v>戴凌龙</x:v>
+        <x:v>陶晓明</x:v>
       </x:c>
       <x:c r="B55" s="6" t="str">
-        <x:v>institution-classification-13</x:v>
+        <x:v>taoxiaoming-source-3</x:v>
       </x:c>
       <x:c r="C55" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://newetds.lib.tsinghua.edu.cn/qh/paper/summary?dbCode=ETDQH&amp;sysId=173003</x:v>
       </x:c>
       <x:c r="D55" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E55" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6897,16 +8779,16 @@
     </x:row>
     <x:row r="56" ht="64" customHeight="1">
       <x:c r="A56" s="6" t="str">
-        <x:v>戴凌龙</x:v>
+        <x:v>陶晓明</x:v>
       </x:c>
       <x:c r="B56" s="6" t="str">
-        <x:v>institution-classification-14</x:v>
+        <x:v>taoxiaoming-source-4</x:v>
       </x:c>
       <x:c r="C56" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
       </x:c>
       <x:c r="D56" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E56" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6920,16 +8802,16 @@
     </x:row>
     <x:row r="57" ht="64" customHeight="1">
       <x:c r="A57" s="6" t="str">
-        <x:v>樊平毅</x:v>
+        <x:v>陶晓明</x:v>
       </x:c>
       <x:c r="B57" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>taoxiaoming-source-5</x:v>
       </x:c>
       <x:c r="C57" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://www.tsinghua.edu.cn/info/1167/93854.htm</x:v>
       </x:c>
       <x:c r="D57" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E57" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6943,16 +8825,16 @@
     </x:row>
     <x:row r="58" ht="64" customHeight="1">
       <x:c r="A58" s="6" t="str">
-        <x:v>樊平毅</x:v>
+        <x:v>王劲涛</x:v>
       </x:c>
       <x:c r="B58" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>wangjingtao-source-1</x:v>
       </x:c>
       <x:c r="C58" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2.htm</x:v>
       </x:c>
       <x:c r="D58" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E58" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6966,16 +8848,16 @@
     </x:row>
     <x:row r="59" ht="64" customHeight="1">
       <x:c r="A59" s="6" t="str">
-        <x:v>冯伟</x:v>
+        <x:v>王劲涛</x:v>
       </x:c>
       <x:c r="B59" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>wangjingtao-source-2</x:v>
       </x:c>
       <x:c r="C59" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjingtao/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D59" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E59" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -6989,16 +8871,16 @@
     </x:row>
     <x:row r="60" ht="64" customHeight="1">
       <x:c r="A60" s="6" t="str">
-        <x:v>葛宁</x:v>
+        <x:v>王劲涛</x:v>
       </x:c>
       <x:c r="B60" s="6" t="str">
-        <x:v>institution-classification-7</x:v>
+        <x:v>wangjingtao-source-3</x:v>
       </x:c>
       <x:c r="C60" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://vtsociety.org/contact/jintao-wang</x:v>
       </x:c>
       <x:c r="D60" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E60" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7012,16 +8894,16 @@
     </x:row>
     <x:row r="61" ht="64" customHeight="1">
       <x:c r="A61" s="6" t="str">
-        <x:v>葛宁</x:v>
+        <x:v>王劲涛</x:v>
       </x:c>
       <x:c r="B61" s="6" t="str">
-        <x:v>institution-classification-8</x:v>
+        <x:v>wangjingtao-source-4</x:v>
       </x:c>
       <x:c r="C61" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
       </x:c>
       <x:c r="D61" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E61" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7035,16 +8917,16 @@
     </x:row>
     <x:row r="62" ht="64" customHeight="1">
       <x:c r="A62" s="6" t="str">
-        <x:v>谷源涛</x:v>
+        <x:v>王军</x:v>
       </x:c>
       <x:c r="B62" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>wangjun-source-1</x:v>
       </x:c>
       <x:c r="C62" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2/1.htm</x:v>
       </x:c>
       <x:c r="D62" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E62" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7058,16 +8940,16 @@
     </x:row>
     <x:row r="63" ht="64" customHeight="1">
       <x:c r="A63" s="6" t="str">
-        <x:v>谷源涛</x:v>
+        <x:v>王军</x:v>
       </x:c>
       <x:c r="B63" s="6" t="str">
-        <x:v>institution-classification-6</x:v>
+        <x:v>wangjun-source-2</x:v>
       </x:c>
       <x:c r="C63" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/wangjun/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D63" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E63" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7081,16 +8963,16 @@
     </x:row>
     <x:row r="64" ht="64" customHeight="1">
       <x:c r="A64" s="6" t="str">
-        <x:v>李勇</x:v>
+        <x:v>王昭诚</x:v>
       </x:c>
       <x:c r="B64" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>wangzhaocheng-source-1</x:v>
       </x:c>
       <x:c r="C64" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2/1.htm</x:v>
       </x:c>
       <x:c r="D64" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E64" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7104,16 +8986,16 @@
     </x:row>
     <x:row r="65" ht="64" customHeight="1">
       <x:c r="A65" s="6" t="str">
-        <x:v>李勇</x:v>
+        <x:v>王昭诚</x:v>
       </x:c>
       <x:c r="B65" s="6" t="str">
-        <x:v>institution-classification-5</x:v>
+        <x:v>wangzhaocheng-source-2</x:v>
       </x:c>
       <x:c r="C65" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D65" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E65" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7127,16 +9009,16 @@
     </x:row>
     <x:row r="66" ht="64" customHeight="1">
       <x:c r="A66" s="6" t="str">
-        <x:v>陆建华</x:v>
+        <x:v>王昭诚</x:v>
       </x:c>
       <x:c r="B66" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>wangzhaocheng-source-3</x:v>
       </x:c>
       <x:c r="C66" s="6" t="str">
-        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+        <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
       </x:c>
       <x:c r="D66" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
       <x:c r="E66" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7150,16 +9032,16 @@
     </x:row>
     <x:row r="67" ht="64" customHeight="1">
       <x:c r="A67" s="6" t="str">
-        <x:v>陆建华</x:v>
+        <x:v>周世东</x:v>
       </x:c>
       <x:c r="B67" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>zhoushidong-source-1</x:v>
       </x:c>
       <x:c r="C67" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://www.ee.tsinghua.edu.cn/ryqk/teacher/txyjs/js2/1.htm</x:v>
       </x:c>
       <x:c r="D67" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>official_roster_read</x:v>
       </x:c>
       <x:c r="E67" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -7173,31 +9055,514 @@
     </x:row>
     <x:row r="68" ht="64" customHeight="1">
       <x:c r="A68" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="str">
+        <x:v>zhoushidong-source-2</x:v>
+      </x:c>
+      <x:c r="C68" s="6" t="str">
+        <x:v>https://web.ee.tsinghua.edu.cn/zhoushidong/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D68" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F68" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="64" customHeight="1">
+      <x:c r="A69" s="6" t="str">
+        <x:v>陈巍</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C69" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D69" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E69" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F69" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G69" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="64" customHeight="1">
+      <x:c r="A70" s="6" t="str">
+        <x:v>陈巍</x:v>
+      </x:c>
+      <x:c r="B70" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C70" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D70" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F70" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G70" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="64" customHeight="1">
+      <x:c r="A71" s="6" t="str">
+        <x:v>戴凌龙</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="str">
+        <x:v>institution-classification-13</x:v>
+      </x:c>
+      <x:c r="C71" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D71" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F71" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G71" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="64" customHeight="1">
+      <x:c r="A72" s="6" t="str">
+        <x:v>戴凌龙</x:v>
+      </x:c>
+      <x:c r="B72" s="6" t="str">
+        <x:v>institution-classification-14</x:v>
+      </x:c>
+      <x:c r="C72" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D72" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E72" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F72" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G72" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="64" customHeight="1">
+      <x:c r="A73" s="6" t="str">
+        <x:v>樊平毅</x:v>
+      </x:c>
+      <x:c r="B73" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C73" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D73" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E73" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F73" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G73" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="64" customHeight="1">
+      <x:c r="A74" s="6" t="str">
+        <x:v>樊平毅</x:v>
+      </x:c>
+      <x:c r="B74" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C74" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D74" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E74" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F74" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G74" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="64" customHeight="1">
+      <x:c r="A75" s="6" t="str">
+        <x:v>冯伟</x:v>
+      </x:c>
+      <x:c r="B75" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C75" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D75" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E75" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F75" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G75" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="64" customHeight="1">
+      <x:c r="A76" s="6" t="str">
+        <x:v>葛宁</x:v>
+      </x:c>
+      <x:c r="B76" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C76" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D76" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E76" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F76" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G76" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="64" customHeight="1">
+      <x:c r="A77" s="6" t="str">
+        <x:v>葛宁</x:v>
+      </x:c>
+      <x:c r="B77" s="6" t="str">
+        <x:v>institution-classification-8</x:v>
+      </x:c>
+      <x:c r="C77" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D77" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E77" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F77" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G77" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="64" customHeight="1">
+      <x:c r="A78" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B78" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C78" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D78" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E78" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F78" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G78" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="64" customHeight="1">
+      <x:c r="A79" s="6" t="str">
+        <x:v>谷源涛</x:v>
+      </x:c>
+      <x:c r="B79" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C79" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D79" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E79" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F79" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G79" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="64" customHeight="1">
+      <x:c r="A80" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B80" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C80" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D80" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E80" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F80" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G80" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="64" customHeight="1">
+      <x:c r="A81" s="6" t="str">
+        <x:v>李勇</x:v>
+      </x:c>
+      <x:c r="B81" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C81" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D81" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E81" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F81" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G81" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="64" customHeight="1">
+      <x:c r="A82" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B82" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C82" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D82" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E82" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F82" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G82" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="64" customHeight="1">
+      <x:c r="A83" s="6" t="str">
+        <x:v>陆建华</x:v>
+      </x:c>
+      <x:c r="B83" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C83" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D83" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E83" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F83" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G83" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="64" customHeight="1">
+      <x:c r="A84" s="6" t="str">
         <x:v>粟欣</x:v>
       </x:c>
-      <x:c r="B68" s="6" t="str">
+      <x:c r="B84" s="6" t="str">
         <x:v>institution-classification-3</x:v>
       </x:c>
-      <x:c r="C68" s="6" t="str">
+      <x:c r="C84" s="6" t="str">
         <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
       </x:c>
-      <x:c r="D68" s="6" t="str">
+      <x:c r="D84" s="6" t="str">
         <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
       </x:c>
-      <x:c r="E68" s="7" t="d">
-        <x:v>2026-10-23T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="F68" s="6" t="str">
-        <x:v>thu</x:v>
-      </x:c>
-      <x:c r="G68" s="6" t="str">
+      <x:c r="E84" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F84" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G84" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="64" customHeight="1">
+      <x:c r="A85" s="6" t="str">
+        <x:v>陶晓明</x:v>
+      </x:c>
+      <x:c r="B85" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C85" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D85" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E85" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F85" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G85" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="64" customHeight="1">
+      <x:c r="A86" s="6" t="str">
+        <x:v>王劲涛</x:v>
+      </x:c>
+      <x:c r="B86" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C86" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D86" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E86" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F86" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G86" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="64" customHeight="1">
+      <x:c r="A87" s="6" t="str">
+        <x:v>王军</x:v>
+      </x:c>
+      <x:c r="B87" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C87" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D87" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E87" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F87" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G87" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="64" customHeight="1">
+      <x:c r="A88" s="6" t="str">
+        <x:v>王昭诚</x:v>
+      </x:c>
+      <x:c r="B88" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C88" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D88" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E88" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F88" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G88" s="6" t="str">
+        <x:v>清华大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="64" customHeight="1">
+      <x:c r="A89" s="6" t="str">
+        <x:v>周世东</x:v>
+      </x:c>
+      <x:c r="B89" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C89" s="6" t="str">
+        <x:v>https://www.csust.edu.cn/fzgh/info/1016/1662.htm</x:v>
+      </x:c>
+      <x:c r="D89" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E89" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F89" s="6" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="G89" s="6" t="str">
         <x:v>清华大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ad9b20f2a3d41e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f1ebbf317645c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/thu-ee-communications.xlsx
+++ b/site/exports/thu-ee-communications.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf13c36126e814830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Ra913753b3b7140f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rfb918ca988b84739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rc7fed85c4a884d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R8153de0dc7a440fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd1b1b3d5517b4859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R339efabc7fa045c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R35c63ae304034062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rcc7aa35e81f84550"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R0ea4ae8d1d1b4904"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T9_0" displayName="T9_0" ref="A1:K16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T12_0" displayName="T12_0" ref="A1:K16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T9_1" displayName="T9_1" ref="A1:S121" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T12_1" displayName="T12_1" ref="A1:S121" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T9_2" displayName="T9_2" ref="A1:L4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T12_2" displayName="T12_2" ref="A1:L4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T9_3" displayName="T9_3" ref="A1:L28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T12_3" displayName="T12_3" ref="A1:L28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -225,7 +225,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T9_4" displayName="T9_4" ref="A1:G89" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T12_4" displayName="T12_4" ref="A1:G89" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -980,7 +980,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e71ff1cd72048f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd71999f1c8dd4d4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6284,7 +6284,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb6a2e509ef14d64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0060d9cdaf4e72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6458,7 +6458,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebc55b8a2b674274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7477e40e842843e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6536,7 +6536,7 @@
         <x:v>https://www.ee.cityu.edu.hk/~lindai/32_Resource_Allocation_in_Cooperative_Networks_IEEE_TWireless.pdf</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>https://www.ee.cityu.edu.hk/~lindai/32_Resource_Allocation_in_Cooperative_Networks_IEEE_TWireless.pdf</x:v>
@@ -6545,7 +6545,7 @@
         <x:v>https://www.ee.cityu.edu.hk/~lindai/32_Resource_Allocation_in_Cooperative_Networks_IEEE_TWireless.pdf</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>official_hosted_article_verified</x:v>
+        <x:v>官方托管的单篇文章已核；不代表全量成果或授权复制全文。；official_hosted_article_verified</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
         <x:v>官方高校作者托管全文首页列清华电子系署名，末尾履历与本人清华2002/2007学位和香港科大访问经历匹配；不据合著推导师。</x:v>
@@ -6574,7 +6574,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/paper/MUSE-FM_Multi-Task_Environment-Aware_Foundation_Model_for_Wireless_Communications.pdf</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/publications.html</x:v>
@@ -6583,7 +6583,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/paper/MUSE-FM_Multi-Task_Environment-Aware_Foundation_Model_for_Wireless_Communications.pdf</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>official_hosted_article_verified</x:v>
+        <x:v>官方托管的单篇文章已核；不代表全量成果或授权复制全文。；official_hosted_article_verified</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
         <x:v>个人官方论文列表[J144]及单篇公开PDF双核；仅存书目。</x:v>
@@ -6612,7 +6612,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/paper/Wavenumber-Domain_Signal_Processing_for_Holographic_MIMO_Foundations_Methods_and_Future_Directions.pdf</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/publications.html</x:v>
@@ -6621,7 +6621,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/paper/Wavenumber-Domain_Signal_Processing_for_Holographic_MIMO_Foundations_Methods_and_Future_Directions.pdf</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str">
-        <x:v>official_hosted_article_verified</x:v>
+        <x:v>官方托管的单篇文章已核；不代表全量成果或授权复制全文。；official_hosted_article_verified</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str">
         <x:v>个人官方论文列表[J143]及单篇公开PDF双核；仅存书目。</x:v>
@@ -6650,7 +6650,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/paper/Dimension-Independent_Channel_Estimation_for_RIS-Assisted_Communications_From_Cascaded_to_Separate.pdf</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/publications.html</x:v>
@@ -6659,7 +6659,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/dailinglong/publications/paper/Dimension-Independent_Channel_Estimation_for_RIS-Assisted_Communications_From_Cascaded_to_Separate.pdf</x:v>
       </x:c>
       <x:c r="I5" s="6" t="str">
-        <x:v>official_hosted_article_verified</x:v>
+        <x:v>官方托管的单篇文章已核；不代表全量成果或授权复制全文。；official_hosted_article_verified</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str">
         <x:v>个人官方论文列表[J142]及单篇公开PDF双核；仅存书目。</x:v>
@@ -6684,7 +6684,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
@@ -6693,7 +6693,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
         <x:v>官方学术成果页Machine Learning &amp; Mobile Computing首项；该项未列年份、卷页和DOI，不补猜。</x:v>
@@ -6718,7 +6718,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
@@ -6727,7 +6727,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
       </x:c>
       <x:c r="I7" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str">
         <x:v>同一官方栏目第2项；未列年份、卷页及DOI。</x:v>
@@ -6752,7 +6752,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
@@ -6761,7 +6761,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/fanpingyi/zh_CN/zdylm/5097/list/index.htm</x:v>
       </x:c>
       <x:c r="I8" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J8" s="6" t="str">
         <x:v>同一官方栏目第3项；未列年份、卷页及DOI。</x:v>
@@ -6788,7 +6788,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
@@ -6797,7 +6797,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str">
         <x:v>电子系官方研究成果展示直接列书目；中文专利作者同页写冯伟和葛宁，研究主题与官方本人简介匹配。仅取书目，不收集学生个人资料。第2题原文larges-cale疑有拼写错误，未暗改。</x:v>
@@ -6824,7 +6824,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
@@ -6833,7 +6833,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J10" s="6" t="str">
         <x:v>电子系官方研究成果展示直接列书目；中文专利作者同页写冯伟和葛宁，研究主题与官方本人简介匹配。仅取书目，不收集学生个人资料。第2题原文larges-cale疑有拼写错误，未暗改。</x:v>
@@ -6860,7 +6860,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
@@ -6869,7 +6869,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J11" s="6" t="str">
         <x:v>电子系官方研究成果展示直接列书目；中文专利作者同页写冯伟和葛宁，研究主题与官方本人简介匹配。仅取书目，不收集学生个人资料。第2题原文larges-cale疑有拼写错误，未暗改。</x:v>
@@ -6896,7 +6896,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
@@ -6905,7 +6905,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
         <x:v>本人论文页暂无内容，采用电子系官方成果展示中的明确N. Ge书目；同页中文作者与其通信研究方向对应。第2题拼写按原页保留，尚未核单篇DOI。</x:v>
@@ -6932,7 +6932,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
@@ -6941,7 +6941,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J13" s="6" t="str">
         <x:v>本人论文页暂无内容，采用电子系官方成果展示中的明确N. Ge书目；同页中文作者与其通信研究方向对应。第2题拼写按原页保留，尚未核单篇DOI。</x:v>
@@ -6968,7 +6968,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
@@ -6977,7 +6977,7 @@
         <x:v>https://www.ee.tsinghua.edu.cn/info/1039/1240.htm</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J14" s="6" t="str">
         <x:v>本人论文页暂无内容，采用电子系官方成果展示中的明确N. Ge书目；同页中文作者与其通信研究方向对应。第2题拼写按原页保留，尚未核单篇DOI。</x:v>
@@ -7004,7 +7004,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
@@ -7013,7 +7013,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J15" s="6" t="str"/>
       <x:c r="K15" s="6" t="str">
@@ -7038,7 +7038,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
@@ -7047,7 +7047,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I16" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J16" s="6" t="str"/>
       <x:c r="K16" s="6" t="str">
@@ -7072,7 +7072,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/zhym/4434/list/index.htm</x:v>
@@ -7081,7 +7081,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/guyuantao/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J17" s="6" t="str"/>
       <x:c r="K17" s="6" t="str">
@@ -7106,7 +7106,7 @@
         <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
       </x:c>
       <x:c r="F18" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
         <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
@@ -7115,7 +7115,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I18" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J18" s="6" t="str">
         <x:v>实验室清单明确署名Yong Li，精选非全集。</x:v>
@@ -7142,7 +7142,7 @@
         <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
         <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
@@ -7151,7 +7151,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J19" s="6" t="str">
         <x:v>实验室清单明确署名Yong Li，精选非全集。</x:v>
@@ -7178,7 +7178,7 @@
         <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
       </x:c>
       <x:c r="F20" s="6" t="str">
-        <x:v>conference_paper</x:v>
+        <x:v>会议论文；conference_paper</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
         <x:v>https://fi.ee.tsinghua.edu.cn/publications/</x:v>
@@ -7187,7 +7187,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/liyong/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J20" s="6" t="str">
         <x:v>实验室清单明确署名Yong Li，精选非全集。</x:v>
@@ -7214,7 +7214,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
       </x:c>
       <x:c r="F21" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
@@ -7223,7 +7223,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I21" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J21" s="6" t="str">
         <x:v>官网精选书目，无逐篇出版者URL核定。</x:v>
@@ -7250,7 +7250,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
       </x:c>
       <x:c r="F22" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
@@ -7259,7 +7259,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J22" s="6" t="str">
         <x:v>官网精选书目，无逐篇出版者URL核定。</x:v>
@@ -7286,7 +7286,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
       </x:c>
       <x:c r="F23" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/zdylm/5094/list/index.htm</x:v>
@@ -7295,7 +7295,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/niuzhisheng/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J23" s="6" t="str">
         <x:v>官网精选书目，无逐篇出版者URL核定。</x:v>
@@ -7322,7 +7322,7 @@
         <x:v>https://newetds.lib.tsinghua.edu.cn/qh/paper/summary?dbCode=ETDQH&amp;sysId=173003</x:v>
       </x:c>
       <x:c r="F24" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
         <x:v>https://newetds.lib.tsinghua.edu.cn/qh/paper/summary?dbCode=ETDQH&amp;sysId=173003</x:v>
@@ -7331,7 +7331,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J24" s="6" t="str">
         <x:v>公开题录，答辩2008-06-06；不公开全文或学生学号。</x:v>
@@ -7358,7 +7358,7 @@
         <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
       </x:c>
       <x:c r="F25" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
         <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
@@ -7367,7 +7367,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I25" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J25" s="6" t="str">
         <x:v>本人官网精选书目，未逐篇查出版者或补DOI。</x:v>
@@ -7394,7 +7394,7 @@
         <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
       </x:c>
       <x:c r="F26" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
         <x:v>https://it.xju.edu.cn/info/1327/3283.htm</x:v>
@@ -7403,7 +7403,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/taoxiaoming/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I26" s="6" t="str">
-        <x:v>official_publication_list_only</x:v>
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
       </x:c>
       <x:c r="J26" s="6" t="str">
         <x:v>本人官网精选书目，未逐篇查出版者或补DOI。</x:v>
@@ -7432,7 +7432,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
       </x:c>
       <x:c r="F27" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
         <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
@@ -7441,7 +7441,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/wangjingtao/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I27" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J27" s="6" t="str">
         <x:v>清华作者官网论文副本首页署名与机构直接核，非从共同作者推导师。</x:v>
@@ -7470,7 +7470,7 @@
         <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
       </x:c>
       <x:c r="F28" s="6" t="str">
-        <x:v>journal_article</x:v>
+        <x:v>期刊论文；journal_article</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
         <x:v>https://oa.ee.tsinghua.edu.cn/~dailinglong/publications/paper/Spectrum-%20and%20Energy-Efficient%20OFDM%20Based%20on%20Simultaneous%20Multi-Channel%20Reconstruction.pdf</x:v>
@@ -7479,7 +7479,7 @@
         <x:v>https://web.ee.tsinghua.edu.cn/wangzhaocheng/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="I28" s="6" t="str">
-        <x:v>article_metadata_verified</x:v>
+        <x:v>单篇文章书目元数据已核，不表示成果全集或全文复制。；article_metadata_verified</x:v>
       </x:c>
       <x:c r="J28" s="6" t="str">
         <x:v>清华作者官网论文副本首页署名与机构直接核，非从共同作者推导师。</x:v>
@@ -7494,7 +7494,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bfd69f510024194"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read262a41fff49ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9562,7 +9562,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f1ebbf317645c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R913ef99d2f2f46ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/thu-ee-communications.xlsx
+++ b/site/exports/thu-ee-communications.xlsx
@@ -452,8 +452,8 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -867,12 +867,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -920,12 +920,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
